--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,36 +18775,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18820,36 +18808,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18865,36 +18841,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18910,36 +18874,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18955,36 +18907,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19000,36 +18940,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19045,36 +18973,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19090,36 +19006,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19135,36 +19039,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19180,36 +19072,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patrick Cantlay</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19225,36 +19105,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19270,36 +19138,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19315,36 +19171,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19360,36 +19204,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cameron Young</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19405,36 +19237,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19450,36 +19270,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19495,36 +19303,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19540,36 +19336,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19585,36 +19369,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19630,36 +19402,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19675,36 +19435,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19720,36 +19468,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19765,36 +19501,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>26.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19810,36 +19534,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russell Henley</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19855,36 +19567,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19900,36 +19600,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19945,36 +19633,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19990,36 +19666,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -20035,36 +19699,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -20080,36 +19732,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20125,36 +19765,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20170,36 +19798,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20215,36 +19831,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20260,36 +19864,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brandt Snedeker</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20305,36 +19897,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20350,36 +19930,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20395,36 +19963,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20440,36 +19996,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thorbjørn Olesen</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20485,36 +20029,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20530,36 +20062,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20575,36 +20095,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,36 +20128,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20665,36 +20161,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20710,36 +20194,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Si Woo Kim</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20755,36 +20227,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20800,36 +20260,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20845,36 +20293,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20890,36 +20326,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20935,36 +20359,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adrien Saddier</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20980,36 +20392,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -21025,36 +20425,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -21070,36 +20458,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -21115,36 +20491,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Matt Kuchar</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -21160,36 +20524,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -21205,36 +20557,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21250,36 +20590,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21295,36 +20623,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21340,36 +20656,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>J.J. Spaun</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21385,36 +20689,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21430,36 +20722,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21475,36 +20755,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21520,36 +20788,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brian Campbell</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21565,36 +20821,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21610,36 +20854,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nicolai Højgaard</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21655,36 +20887,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21700,36 +20920,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Karl Vilips</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21745,36 +20953,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21790,7 +20986,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -21802,24 +20998,12 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21835,7 +21019,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21847,24 +21031,12 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21880,36 +21052,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>
@@ -21925,36 +21085,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harris English</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>--</t>
@@ -21970,36 +21118,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>--</t>
@@ -22015,36 +21151,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>--</t>
@@ -22060,26 +21184,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -22097,26 +21217,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -22134,26 +21250,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -22171,26 +21283,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -22208,26 +21316,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -22245,26 +21349,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -22282,26 +21382,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -22319,26 +21415,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ben Griffin</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -22356,26 +21448,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -22393,26 +21481,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jake Knapp</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -22430,26 +21514,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>William Jennings</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -22467,26 +21547,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -22504,26 +21580,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -22541,26 +21613,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -22578,26 +21646,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -22615,26 +21679,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -22652,26 +21712,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -22689,26 +21745,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -22726,26 +21778,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Akshay Bhatia</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
     </row>
@@ -22758,7 +21806,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -22770,14 +21818,10 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
     </row>
@@ -22790,7 +21834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -22802,14 +21846,10 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
     </row>
@@ -22822,7 +21862,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -22834,14 +21874,10 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
     </row>
@@ -22854,7 +21890,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -22866,14 +21902,10 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
     </row>
@@ -22898,14 +21930,10 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
     </row>
@@ -22918,7 +21946,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -22930,14 +21958,10 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
     </row>
@@ -22950,7 +21974,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22962,14 +21986,10 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
     </row>
@@ -22982,7 +22002,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ryan Ruffels</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22994,14 +22014,10 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
     </row>
@@ -23014,7 +22030,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -23026,14 +22042,10 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
     </row>
@@ -23046,7 +22058,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sam Stevens</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -23058,14 +22070,10 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
     </row>
@@ -23078,7 +22086,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -23090,14 +22098,10 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
     </row>
@@ -23110,7 +22114,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -23122,14 +22126,10 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
     </row>
@@ -23142,26 +22142,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
     </row>
@@ -23174,26 +22170,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
     </row>
@@ -23206,26 +22198,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
     </row>
@@ -23238,26 +22226,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
     </row>
@@ -23270,26 +22254,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
     </row>
@@ -23302,26 +22282,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
     </row>
@@ -23334,26 +22310,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
     </row>
@@ -23366,26 +22338,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chris Gotterup</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
     </row>
@@ -23398,26 +22366,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
     </row>
@@ -23430,26 +22394,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Webb Simpson</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
     </row>
@@ -23462,26 +22422,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
     </row>
@@ -23494,26 +22450,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Zach J. Johnson</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
     </row>
@@ -23526,26 +22478,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
     </row>
@@ -23558,26 +22506,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
     </row>
@@ -23590,26 +22534,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
     </row>
@@ -23622,893 +22562,52 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Kevin Streelman</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Stefano Mazzoli</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Cam Davis</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Matti Schmid</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Séamus Power</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Lucas Glover</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Patton Kizzire</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Max McGreevy</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr"/>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Chad Ramey</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Daniel Azallion</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Pontus Nyholm</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Nick Dunlap</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr"/>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Christo Lamprecht</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Wyndham Clark</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Lanto Griffin</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Brendon Todd</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Ryan Celano</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Andrew Novak</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Patrick Wilkes-Krier</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr"/>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Steven Fisk</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Justin Quiban</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Joe Hooks</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Keenan Huskey</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Alejandro Tosti</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Austin Smotherman</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Brad Dalke</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>+16</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Patrick Rodgers</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-    </row>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18693,7 +18693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.140625" bestFit="1" customWidth="1" style="37" min="1" max="1"/>
@@ -18775,19 +18775,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -18808,19 +18808,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -18841,19 +18841,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -18874,19 +18874,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -18907,19 +18907,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -18973,19 +18973,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -19006,19 +19006,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -19039,19 +19039,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -19072,19 +19072,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -19105,19 +19105,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -19138,19 +19138,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -19171,19 +19171,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -19204,19 +19204,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -19270,19 +19270,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -19303,19 +19303,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -19336,19 +19336,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -19369,19 +19369,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19402,19 +19402,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -19435,19 +19435,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -19468,19 +19468,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -19534,19 +19534,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -19567,19 +19567,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -19600,19 +19600,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -19633,19 +19633,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -19666,19 +19666,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,19 +19699,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,19 +19732,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -19765,19 +19765,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -19803,14 +19803,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -19831,19 +19831,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -19864,19 +19864,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -19897,19 +19897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19930,19 +19930,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -19963,19 +19963,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19996,19 +19996,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -20029,19 +20029,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -20062,19 +20062,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -20095,19 +20095,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -20128,19 +20128,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -20161,19 +20161,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Matt Snyder</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20194,19 +20194,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -20227,19 +20227,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -20260,19 +20260,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -20293,19 +20293,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -20326,19 +20326,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -20359,19 +20359,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -20392,19 +20392,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -20425,19 +20425,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -20458,19 +20458,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -20491,19 +20491,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -20524,19 +20524,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -20557,19 +20557,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -20590,19 +20590,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -20623,19 +20623,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -20656,19 +20656,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -20689,19 +20689,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -20722,19 +20722,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -20755,19 +20755,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -20788,19 +20788,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -20826,14 +20826,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -20854,19 +20854,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -20887,19 +20887,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -20920,19 +20920,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -20986,19 +20986,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -21019,19 +21019,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -21052,19 +21052,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -21085,19 +21085,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -21118,19 +21118,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -21151,19 +21151,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21196,7 +21196,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21229,7 +21229,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21262,7 +21262,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -21283,7 +21283,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21295,7 +21295,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21328,7 +21328,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21361,7 +21361,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21394,7 +21394,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -21427,7 +21427,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -21460,7 +21460,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -21493,7 +21493,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21526,7 +21526,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -21559,7 +21559,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -21580,7 +21580,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21592,7 +21592,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -21613,7 +21613,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -21625,7 +21625,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -21658,7 +21658,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -21679,7 +21679,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21691,7 +21691,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -21712,7 +21712,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21724,7 +21724,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21757,7 +21757,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21790,7 +21790,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21818,7 +21818,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21874,7 +21874,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21902,7 +21902,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21930,7 +21930,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Zach J. Johnson</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21958,7 +21958,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21986,7 +21986,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -22002,19 +22002,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -22030,19 +22030,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -22058,19 +22058,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -22086,19 +22086,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -22114,19 +22114,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rhett Rasmussen</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -22142,19 +22142,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -22170,19 +22170,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -22198,19 +22198,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -22226,19 +22226,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -22259,14 +22259,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -22282,19 +22282,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -22310,19 +22310,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -22338,19 +22338,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tyson Shelley</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -22366,19 +22366,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -22394,19 +22394,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston Bracken</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -22422,19 +22422,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -22450,19 +22450,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Zach J. Johnson</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -22478,19 +22478,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -22506,19 +22506,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -22534,19 +22534,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -22562,52 +22562,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
     </row>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,19 +18775,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18907,19 +18907,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -18973,19 +18973,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -19006,19 +19006,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -19039,19 +19039,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -19072,19 +19072,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -19105,19 +19105,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -19138,19 +19138,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -19171,19 +19171,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -19204,19 +19204,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -19270,19 +19270,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -19303,19 +19303,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -19336,19 +19336,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -19369,19 +19369,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19402,19 +19402,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -19435,19 +19435,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -19468,19 +19468,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -19534,19 +19534,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -19567,19 +19567,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -19600,19 +19600,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -19633,19 +19633,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -19666,19 +19666,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,19 +19699,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,19 +19732,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -19765,19 +19765,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -19798,19 +19798,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -19831,19 +19831,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -19864,19 +19864,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -19897,19 +19897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19930,19 +19930,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -19963,19 +19963,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19996,19 +19996,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -20029,19 +20029,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -20062,19 +20062,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -20095,19 +20095,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -20128,19 +20128,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -20161,19 +20161,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20194,19 +20194,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -20227,19 +20227,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -20260,19 +20260,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -20293,19 +20293,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -20326,19 +20326,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -20359,19 +20359,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -20392,19 +20392,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -20425,19 +20425,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston Bracken</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -20458,19 +20458,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -20491,19 +20491,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -20524,19 +20524,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -20557,19 +20557,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -20590,19 +20590,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -20623,19 +20623,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -20656,19 +20656,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -20689,19 +20689,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -20722,19 +20722,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -20755,19 +20755,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -20788,19 +20788,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -20821,19 +20821,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -20854,19 +20854,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -20887,19 +20887,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -20920,19 +20920,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -20986,19 +20986,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -21019,19 +21019,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -21052,19 +21052,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -21085,19 +21085,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -21118,19 +21118,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -21151,19 +21151,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -21184,19 +21184,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -21217,19 +21217,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -21250,19 +21250,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -21283,19 +21283,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -21316,19 +21316,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -21349,19 +21349,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -21382,19 +21382,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -21415,19 +21415,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -21448,19 +21448,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -21481,19 +21481,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -21514,19 +21514,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -21547,19 +21547,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -21580,19 +21580,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -21613,19 +21613,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -21646,19 +21646,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -21679,19 +21679,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -21712,19 +21712,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rhett Rasmussen</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -21745,19 +21745,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -21778,19 +21778,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -21806,19 +21806,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -21834,19 +21834,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -21862,19 +21862,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tyson Shelley</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -21890,19 +21890,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -21918,19 +21918,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -21951,14 +21951,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -21974,19 +21974,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -22002,19 +22002,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -22030,19 +22030,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -22058,19 +22058,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -22086,19 +22086,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -22114,19 +22114,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22154,7 +22154,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -22182,7 +22182,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -22198,7 +22198,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22238,7 +22238,7 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22266,7 +22266,7 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22350,7 +22350,7 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -22366,19 +22366,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -22394,7 +22394,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Matt Snyder</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -22462,7 +22462,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -22490,7 +22490,7 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -22534,19 +22534,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -22562,19 +22562,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,22 +18775,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -18808,12 +18812,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18823,7 +18827,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -18841,12 +18849,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18856,7 +18864,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
@@ -18874,22 +18886,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -18907,22 +18923,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -18940,22 +18960,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -18973,22 +18997,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -19006,22 +19034,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -19039,22 +19071,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -19072,7 +19108,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19084,10 +19120,14 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -19105,22 +19145,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -19138,12 +19182,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -19153,7 +19197,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -19171,22 +19219,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -19204,22 +19256,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -19237,22 +19293,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -19270,22 +19330,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -19303,22 +19367,26 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -19336,12 +19404,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -19351,7 +19419,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -19369,22 +19441,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -19402,22 +19478,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -19435,22 +19515,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -19468,22 +19552,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -19501,22 +19589,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -19534,22 +19626,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -19567,12 +19663,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -19582,7 +19678,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -19600,22 +19700,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -19633,12 +19737,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -19648,7 +19752,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -19666,22 +19774,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -19699,22 +19811,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -19732,22 +19848,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -19765,22 +19885,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -19798,22 +19922,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -19831,22 +19959,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -19869,7 +20001,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -19879,7 +20011,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -19897,22 +20033,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -19930,22 +20070,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -19963,22 +20107,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
@@ -19996,22 +20144,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -20029,22 +20181,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tyson Shelley</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -20062,22 +20218,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -20095,22 +20255,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -20128,12 +20292,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -20143,7 +20307,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -20161,12 +20329,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -20176,7 +20344,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -20194,22 +20366,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -20227,22 +20403,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -20260,12 +20440,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -20275,7 +20455,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -20293,22 +20477,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -20326,22 +20514,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -20359,22 +20551,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -20392,22 +20588,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -20425,22 +20625,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -20458,22 +20662,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -20491,22 +20699,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -20524,22 +20736,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -20557,22 +20773,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -20590,22 +20810,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -20623,22 +20847,26 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -20656,22 +20884,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -20689,22 +20921,26 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -20722,22 +20958,26 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -20755,22 +20995,26 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -20788,22 +21032,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -20821,22 +21069,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -20854,22 +21106,26 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -20887,22 +21143,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -20920,22 +21180,26 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -20953,22 +21217,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -20986,22 +21254,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -21019,22 +21291,26 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -21052,22 +21328,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -21085,22 +21365,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
@@ -21118,22 +21402,26 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -21151,22 +21439,26 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
@@ -21184,22 +21476,26 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -21217,22 +21513,26 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -21250,7 +21550,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21262,10 +21562,14 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -21283,7 +21587,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21295,10 +21599,14 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -21316,7 +21624,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston Bracken</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21328,10 +21636,14 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -21349,7 +21661,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21361,10 +21673,14 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -21382,7 +21698,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21394,10 +21710,14 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -21415,22 +21735,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -21448,22 +21772,26 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -21481,22 +21809,26 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -21514,22 +21846,26 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -21547,22 +21883,26 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -21580,22 +21920,26 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -21613,22 +21957,26 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -21646,22 +21994,26 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -21679,7 +22031,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21694,7 +22046,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -21712,7 +22068,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21727,7 +22083,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -21745,7 +22105,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21760,7 +22120,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -21778,7 +22142,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21793,7 +22157,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
     </row>
@@ -21806,7 +22174,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21821,7 +22189,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
     </row>
@@ -21834,7 +22206,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21849,7 +22221,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
     </row>
@@ -21862,7 +22238,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21877,7 +22253,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
     </row>
@@ -21890,7 +22270,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21905,7 +22285,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
     </row>
@@ -21918,7 +22302,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21933,7 +22317,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
     </row>
@@ -21946,7 +22334,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zach J. Johnson</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21961,7 +22349,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
     </row>
@@ -21974,7 +22366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21989,7 +22381,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
     </row>
@@ -22002,22 +22398,26 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
     </row>
@@ -22030,7 +22430,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22045,7 +22445,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
     </row>
@@ -22058,7 +22462,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22070,10 +22474,14 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
     </row>
@@ -22086,7 +22494,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Zach J. Johnson</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -22098,10 +22506,14 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
     </row>
@@ -22114,7 +22526,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22129,7 +22541,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
     </row>
@@ -22142,22 +22558,26 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
     </row>
@@ -22170,22 +22590,26 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
     </row>
@@ -22198,7 +22622,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -22213,7 +22637,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
     </row>
@@ -22226,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rhett Rasmussen</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22241,7 +22669,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
     </row>
@@ -22254,22 +22686,26 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
     </row>
@@ -22282,7 +22718,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22297,7 +22733,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
     </row>
@@ -22310,12 +22750,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -22325,7 +22765,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
     </row>
@@ -22338,22 +22782,26 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
     </row>
@@ -22366,7 +22814,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22378,10 +22826,14 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
     </row>
@@ -22394,7 +22846,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Matt Snyder</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -22406,10 +22858,14 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
     </row>
@@ -22422,7 +22878,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22437,7 +22893,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
     </row>
@@ -22450,7 +22910,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -22465,7 +22925,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
     </row>
@@ -22478,22 +22942,26 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
     </row>
@@ -22506,22 +22974,26 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
     </row>
@@ -22534,22 +23006,26 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
     </row>
@@ -22577,7 +23053,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
     </row>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,12 +18775,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -18812,12 +18812,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18829,7 +18829,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -18849,12 +18849,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -18886,24 +18886,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -18923,24 +18923,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -18960,24 +18960,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -18997,24 +18997,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -19034,24 +19034,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -19071,24 +19071,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -19108,24 +19108,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -19145,24 +19145,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -19182,24 +19182,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -19219,24 +19219,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -19256,24 +19256,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -19293,24 +19293,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -19330,24 +19330,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -19367,12 +19367,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -19404,24 +19404,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -19441,24 +19441,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -19478,24 +19478,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -19515,24 +19515,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -19552,24 +19552,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -19589,12 +19589,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -19606,7 +19606,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -19626,24 +19626,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -19663,12 +19663,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -19700,24 +19700,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -19737,24 +19737,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -19774,24 +19774,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -19811,24 +19811,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -19848,24 +19848,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -19885,24 +19885,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -19922,24 +19922,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -19959,24 +19959,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>62.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -19996,24 +19996,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -20033,24 +20033,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -20070,24 +20070,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -20107,24 +20107,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -20144,24 +20144,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -20181,24 +20181,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -20218,24 +20218,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -20255,24 +20255,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -20292,24 +20292,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -20329,24 +20329,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -20366,24 +20366,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -20403,24 +20403,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>32.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -20440,12 +20440,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -20477,12 +20477,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -20514,24 +20514,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -20551,24 +20551,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -20588,12 +20588,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -20605,7 +20605,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -20625,12 +20625,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -20662,24 +20662,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -20699,12 +20699,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -20716,7 +20716,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -20736,12 +20736,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -20773,24 +20773,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -20810,24 +20810,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -20847,24 +20847,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -20884,24 +20884,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -20921,24 +20921,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -20958,12 +20958,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -20995,12 +20995,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -21032,12 +21032,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -21069,12 +21069,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -21106,12 +21106,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -21143,24 +21143,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -21180,24 +21180,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -21217,24 +21217,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -21254,24 +21254,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -21291,12 +21291,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -21328,24 +21328,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -21365,24 +21365,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -21402,24 +21402,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -21439,12 +21439,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -21456,7 +21456,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -21476,24 +21476,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -21513,24 +21513,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -21550,12 +21550,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -21587,24 +21587,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -21624,24 +21624,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -21661,24 +21661,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -21698,24 +21698,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -21735,24 +21735,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tyson Shelley</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -21772,24 +21772,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -21809,12 +21809,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -21826,7 +21826,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -21846,24 +21846,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -21895,12 +21895,12 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -21920,7 +21920,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21932,12 +21932,12 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -21957,7 +21957,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -21969,12 +21969,12 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -21994,7 +21994,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -22048,7 +22048,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -22068,12 +22068,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -22105,24 +22105,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -22142,12 +22142,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -22174,12 +22174,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -22191,7 +22191,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -22206,24 +22206,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -22250,12 +22250,12 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -22282,12 +22282,12 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -22346,12 +22346,12 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -22366,7 +22366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22378,12 +22378,12 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -22447,7 +22447,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -22462,24 +22462,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -22494,24 +22494,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Zach J. Johnson</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22538,12 +22538,12 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22570,12 +22570,12 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -22590,7 +22590,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -22602,12 +22602,12 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -22622,24 +22622,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Zach J. Johnson</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22666,12 +22666,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22698,12 +22698,12 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -22718,7 +22718,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22730,12 +22730,12 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -22750,24 +22750,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -22799,7 +22799,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rhett Rasmussen</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22826,12 +22826,12 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston Bracken</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -22858,12 +22858,12 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22890,12 +22890,12 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -22910,24 +22910,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Matt Snyder</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -22942,24 +22942,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -22974,24 +22974,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18861,12 +18861,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -18886,12 +18886,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -18923,24 +18923,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>52.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -18960,24 +18960,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -18997,24 +18997,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -19034,24 +19034,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -19071,24 +19071,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -19108,19 +19108,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19145,19 +19145,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -19182,24 +19182,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -19219,24 +19219,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -19256,24 +19256,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -19293,19 +19293,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -19330,24 +19330,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -19367,24 +19367,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -19404,24 +19404,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -19441,24 +19441,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -19495,7 +19495,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -19515,19 +19515,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -19552,19 +19552,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -19589,24 +19589,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>63.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19638,12 +19638,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19675,12 +19675,12 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19712,12 +19712,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19749,12 +19749,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -19774,24 +19774,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -19811,24 +19811,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -19848,24 +19848,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -19885,24 +19885,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -19922,24 +19922,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>66.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -19959,19 +19959,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -19996,24 +19996,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20045,12 +20045,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20082,12 +20082,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20119,12 +20119,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -20144,12 +20144,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -20181,24 +20181,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -20218,24 +20218,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -20255,24 +20255,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -20292,24 +20292,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -20329,24 +20329,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -20366,24 +20366,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -20403,24 +20403,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -20440,19 +20440,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -20477,24 +20477,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -20514,24 +20514,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -20551,24 +20551,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -20588,24 +20588,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>39.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -20625,24 +20625,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -20662,24 +20662,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -20699,24 +20699,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -20736,12 +20736,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -20773,24 +20773,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -20822,12 +20822,12 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -20859,12 +20859,12 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -20884,24 +20884,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -20921,19 +20921,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -20958,12 +20958,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -20995,19 +20995,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -21032,12 +21032,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -21069,12 +21069,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -21086,7 +21086,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -21106,19 +21106,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -21143,24 +21143,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -21180,12 +21180,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -21217,24 +21217,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -21254,24 +21254,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21303,12 +21303,12 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -21340,12 +21340,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -21365,24 +21365,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -21402,12 +21402,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -21439,24 +21439,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -21476,24 +21476,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -21513,24 +21513,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -21550,24 +21550,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -21587,24 +21587,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -21624,12 +21624,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -21641,7 +21641,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -21661,24 +21661,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>32.0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -21698,24 +21698,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -21735,24 +21735,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -21772,24 +21772,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Joe Highsmith</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -21809,24 +21809,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -21846,24 +21846,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -21883,24 +21883,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -21920,24 +21920,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -21957,12 +21957,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -21994,24 +21994,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -22031,24 +22031,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -22068,24 +22068,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -22105,24 +22105,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -22142,12 +22142,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -22174,24 +22174,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>29.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -22206,24 +22206,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -22238,24 +22238,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -22270,24 +22270,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -22302,24 +22302,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -22334,24 +22334,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -22366,24 +22366,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -22398,24 +22398,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -22430,24 +22430,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -22462,24 +22462,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -22506,12 +22506,12 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -22526,24 +22526,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -22558,24 +22558,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -22590,24 +22590,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Joe Highsmith</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -22622,24 +22622,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -22654,12 +22654,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Zach J. Johnson</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -22671,7 +22671,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22686,24 +22686,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rhett Rasmussen</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -22718,12 +22718,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Zach J. Johnson</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -22735,7 +22735,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -22750,7 +22750,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Rhett Rasmussen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22762,12 +22762,12 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston Bracken</t>
+          <t>Rasmus Højgaard</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22826,12 +22826,12 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tyson Shelley</t>
+          <t>Boston Bracken</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -22858,12 +22858,12 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>Tyson Shelley</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22890,12 +22890,12 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -22942,24 +22942,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Matt Snyder</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -22974,24 +22974,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rasmus Højgaard</t>
+          <t>Matt Snyder</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -19071,24 +19071,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19120,12 +19120,12 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19231,12 +19231,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>65.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19305,12 +19305,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19527,12 +19527,12 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19564,12 +19564,12 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19601,12 +19601,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -20366,7 +20366,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20378,12 +20378,12 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20452,12 +20452,12 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20489,12 +20489,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -20514,24 +20514,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20563,12 +20563,12 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20637,12 +20637,12 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20674,12 +20674,12 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>68.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -20699,7 +20699,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20748,12 +20748,12 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -20785,12 +20785,12 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -22154,12 +22154,12 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -22186,12 +22186,12 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>70.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -22206,7 +22206,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -22218,12 +22218,12 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -22238,24 +22238,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
           <t>71.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Michael Thompson</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Michael Thompson</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -22346,12 +22346,12 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -22366,7 +22366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22410,12 +22410,12 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Garrick Higgo</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22442,12 +22442,12 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Garrick Higgo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22474,12 +22474,12 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -22622,24 +22622,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Carson Lundell</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Carson Lundell</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22666,12 +22666,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22703,7 +22703,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Seonghyeon An</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -22922,12 +22922,12 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -22942,24 +22942,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seonghyeon An</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -20699,7 +20699,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20711,12 +20711,12 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>68.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -20736,7 +20736,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -20785,12 +20785,12 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -20810,24 +20810,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -20847,24 +20847,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -20933,12 +20933,12 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -20970,12 +20970,12 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21007,12 +21007,12 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -21044,12 +21044,12 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -21081,12 +21081,12 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21118,12 +21118,12 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21155,12 +21155,12 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -21180,7 +21180,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -21229,12 +21229,12 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -21266,12 +21266,12 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -21291,24 +21291,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -21328,24 +21328,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -21377,12 +21377,12 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21488,12 +21488,12 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21525,12 +21525,12 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -21550,7 +21550,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21599,12 +21599,12 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -21624,7 +21624,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21636,12 +21636,12 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21698,7 +21698,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21710,12 +21710,12 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -21747,12 +21747,12 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Bowen Mauss</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22666,12 +22666,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bowen Mauss</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22698,12 +22698,12 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18795,7 +18795,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -18832,7 +18836,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
@@ -18849,7 +18857,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18861,15 +18869,19 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -18886,7 +18898,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18903,10 +18915,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -18923,27 +18939,31 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
@@ -18960,12 +18980,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -18977,10 +18997,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
@@ -18997,27 +19021,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -19034,19 +19062,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19054,7 +19082,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
@@ -19071,27 +19103,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -19108,27 +19144,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -19145,27 +19185,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -19182,12 +19226,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -19199,10 +19243,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -19219,27 +19267,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -19256,27 +19308,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -19293,27 +19349,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
@@ -19330,27 +19390,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
@@ -19372,7 +19436,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19387,7 +19451,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -19404,19 +19472,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -19424,7 +19492,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
@@ -19441,27 +19513,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -19478,27 +19554,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -19515,19 +19595,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -19535,7 +19615,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
@@ -19552,19 +19636,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -19572,7 +19656,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -19589,27 +19677,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -19626,27 +19718,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -19663,27 +19759,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -19700,27 +19800,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -19737,27 +19841,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -19774,27 +19882,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -19811,27 +19923,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -19848,27 +19964,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -19885,27 +20005,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -19922,27 +20046,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -19959,27 +20087,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -19996,27 +20128,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -20033,27 +20169,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -20070,27 +20210,31 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -20107,27 +20251,31 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -20144,19 +20292,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -20164,7 +20312,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -20181,27 +20333,31 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
@@ -20218,27 +20374,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
@@ -20255,27 +20415,31 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
@@ -20292,27 +20456,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
@@ -20329,27 +20497,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
@@ -20366,7 +20538,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20378,15 +20550,19 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
@@ -20403,7 +20579,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20420,10 +20596,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
@@ -20440,7 +20620,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20452,15 +20632,19 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
@@ -20477,7 +20661,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20489,15 +20673,19 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
@@ -20514,7 +20702,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20526,15 +20714,19 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -20551,27 +20743,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -20588,27 +20784,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -20625,7 +20825,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20642,10 +20842,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
@@ -20662,7 +20866,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20674,15 +20878,19 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
@@ -20699,7 +20907,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20711,15 +20919,19 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
@@ -20736,7 +20948,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20748,15 +20960,19 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
@@ -20773,7 +20989,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -20790,10 +21006,14 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
@@ -20810,7 +21030,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -20822,15 +21042,19 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
@@ -20847,27 +21071,31 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
@@ -20884,7 +21112,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -20896,15 +21124,19 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
@@ -20941,7 +21173,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
@@ -20958,7 +21194,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -20970,15 +21206,19 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
@@ -20995,7 +21235,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21007,15 +21247,19 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
@@ -21032,27 +21276,31 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -21069,27 +21317,31 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
@@ -21106,27 +21358,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
@@ -21143,12 +21399,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -21163,7 +21419,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
@@ -21180,27 +21440,31 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
@@ -21217,27 +21481,31 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
@@ -21254,27 +21522,31 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
@@ -21291,27 +21563,31 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
@@ -21333,7 +21609,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -21348,7 +21624,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
@@ -23006,7 +23286,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -23038,19 +23318,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18780,7 +18780,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18816,29 +18816,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -18898,19 +18898,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -18939,29 +18939,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -18980,29 +18980,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19021,12 +19021,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -19038,12 +19038,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19062,29 +19062,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -19125,7 +19125,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19144,12 +19144,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -19161,12 +19161,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19185,29 +19185,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19226,29 +19226,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>33.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19267,29 +19267,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19308,12 +19308,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -19325,12 +19325,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -19349,29 +19349,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -19390,29 +19390,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -19431,29 +19431,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -19472,29 +19472,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -19513,29 +19513,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -19554,29 +19554,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19595,29 +19595,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -19677,29 +19677,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -19718,19 +19718,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -19759,29 +19759,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -19800,29 +19800,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>37.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -19841,29 +19841,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>37.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -19882,12 +19882,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -19899,12 +19899,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -19923,29 +19923,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -19964,29 +19964,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -20005,29 +20005,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -20046,29 +20046,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -20087,29 +20087,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -20128,29 +20128,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -20169,29 +20169,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -20210,12 +20210,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -20227,12 +20227,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -20292,29 +20292,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -20333,29 +20333,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -20374,29 +20374,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -20415,29 +20415,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -20456,12 +20456,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -20473,12 +20473,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>29.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -20497,29 +20497,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -20538,29 +20538,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>40.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -20579,29 +20579,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -20661,29 +20661,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>22.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -20702,29 +20702,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -20743,12 +20743,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -20760,12 +20760,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>22.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -20784,29 +20784,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -20825,29 +20825,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -20866,19 +20866,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -20907,19 +20907,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -20948,29 +20948,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -20989,29 +20989,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -21030,12 +21030,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -21047,12 +21047,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -21088,12 +21088,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -21112,29 +21112,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>16.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -21153,29 +21153,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>12.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,29 +21194,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -21235,29 +21235,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,12 +21276,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -21293,12 +21293,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,29 +21317,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,19 +21358,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21399,29 +21399,29 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,29 +21440,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,29 +21481,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,29 +21522,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21575,17 +21575,17 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21604,29 +21604,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18800,7 +18800,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18841,7 +18845,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18857,7 +18865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18869,20 +18877,24 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18898,7 +18910,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18910,20 +18922,24 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18964,7 +18980,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19005,7 +19025,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19046,7 +19070,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19087,7 +19115,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19128,7 +19160,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19169,7 +19205,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19210,7 +19250,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19251,7 +19295,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19267,7 +19315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19279,20 +19327,24 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19333,7 +19385,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19349,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19366,15 +19422,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19390,12 +19450,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -19407,15 +19467,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19431,7 +19495,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19443,20 +19507,24 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19472,7 +19540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19484,20 +19552,24 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19513,7 +19585,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19525,20 +19597,24 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19554,7 +19630,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19566,20 +19642,24 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19595,32 +19675,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19636,32 +19720,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19677,12 +19765,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -19694,15 +19782,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19718,7 +19810,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19730,12 +19822,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -19743,7 +19835,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19759,7 +19855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19771,20 +19867,24 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19800,24 +19900,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -19825,7 +19925,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19841,12 +19945,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -19858,15 +19962,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19882,19 +19990,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -19904,10 +20012,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -19923,32 +20035,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -19964,32 +20080,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20005,32 +20125,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20046,32 +20170,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20087,7 +20215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20099,20 +20227,24 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20128,7 +20260,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20140,20 +20272,24 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20169,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20181,20 +20317,24 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20210,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20222,20 +20362,24 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20251,7 +20395,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20263,20 +20407,24 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20292,7 +20440,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20304,20 +20452,24 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20333,32 +20485,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20374,19 +20530,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -20399,7 +20555,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20415,12 +20575,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -20432,15 +20592,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20456,32 +20620,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20497,32 +20665,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20538,24 +20710,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -20563,7 +20735,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20579,12 +20755,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -20596,7 +20772,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -20604,7 +20780,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,32 +20800,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20661,32 +20845,36 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20702,24 +20890,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -20727,7 +20915,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20743,19 +20935,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -20765,10 +20957,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20784,19 +20980,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -20806,10 +21002,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -20825,19 +21025,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -20847,10 +21047,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -20866,32 +21070,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -20907,32 +21115,36 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -20948,32 +21160,36 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -20989,32 +21205,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21035,7 +21255,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -21055,7 +21275,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21071,12 +21295,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -21093,10 +21317,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21112,12 +21340,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -21129,15 +21357,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21153,24 +21385,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -21178,7 +21410,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21194,32 +21430,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21235,32 +21475,36 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21276,32 +21520,36 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21322,7 +21570,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -21342,7 +21590,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21358,32 +21610,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21424,7 +21680,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21440,32 +21700,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21481,32 +21745,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21547,7 +21815,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21588,7 +21860,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21604,7 +21880,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Marco Penge</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -21616,20 +21892,24 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18780,7 +18780,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -18865,34 +18865,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -18910,34 +18910,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -18982,7 +18982,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -19000,34 +19000,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -19045,34 +19045,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -19090,34 +19090,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -19135,12 +19135,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -19152,17 +19152,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -19180,34 +19180,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -19225,34 +19225,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19270,34 +19270,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -19315,34 +19315,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -19387,7 +19387,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19405,34 +19405,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -19450,12 +19450,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -19467,17 +19467,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -19495,34 +19495,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -19540,34 +19540,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -19585,34 +19585,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19630,34 +19630,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -19675,34 +19675,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -19720,24 +19720,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19765,34 +19765,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19810,34 +19810,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19855,34 +19855,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19900,24 +19900,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19945,19 +19945,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -19967,12 +19967,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19990,34 +19990,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -20035,34 +20035,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -20080,34 +20080,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -20125,34 +20125,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20170,34 +20170,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20215,34 +20215,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -20260,19 +20260,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -20282,12 +20282,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -20305,34 +20305,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -20350,19 +20350,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -20372,12 +20372,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20395,34 +20395,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20440,34 +20440,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -20512,7 +20512,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20530,34 +20530,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20575,12 +20575,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20620,34 +20620,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20665,34 +20665,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20710,34 +20710,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20755,34 +20755,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>63.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20800,24 +20800,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20845,34 +20845,34 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -20890,12 +20890,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -20935,19 +20935,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -20957,12 +20957,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -20980,24 +20980,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21025,34 +21025,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -21082,22 +21082,22 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21115,34 +21115,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21160,24 +21160,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21205,34 +21205,34 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21250,34 +21250,34 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>35.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -21295,34 +21295,34 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>28.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21340,24 +21340,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -21367,7 +21367,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21385,34 +21385,34 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -21430,34 +21430,34 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -21475,34 +21475,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -21520,34 +21520,34 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -21565,34 +21565,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -21655,19 +21655,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Jackson Koivun</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21677,12 +21677,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -21700,34 +21700,34 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -21745,12 +21745,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -21762,7 +21762,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -21790,7 +21790,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -21802,22 +21802,22 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -21835,34 +21835,34 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -21885,7 +21885,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18780,7 +18780,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18832,14 +18832,14 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>64.0</t>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -18865,34 +18865,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -18910,34 +18910,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -18955,34 +18955,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -19000,19 +19000,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -19045,19 +19045,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -19067,12 +19067,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -19090,34 +19090,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -19135,34 +19135,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -19180,34 +19180,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -19225,34 +19225,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>39.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19270,34 +19270,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -19315,12 +19315,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -19332,17 +19332,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19360,34 +19360,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>21.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19405,34 +19405,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -19450,34 +19450,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -19495,34 +19495,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -19540,12 +19540,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -19557,17 +19557,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -19585,34 +19585,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>64.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>55.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19630,34 +19630,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -19675,34 +19675,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -19720,34 +19720,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19765,34 +19765,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19810,19 +19810,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -19832,12 +19832,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19855,34 +19855,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>30.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19912,22 +19912,22 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19957,7 +19957,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -19967,12 +19967,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19990,24 +19990,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -20035,34 +20035,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -20080,19 +20080,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -20102,12 +20102,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>66.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20137,7 +20137,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -20147,12 +20147,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20182,12 +20182,12 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20227,22 +20227,22 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>42.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20272,22 +20272,22 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20317,22 +20317,22 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -20350,34 +20350,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20395,12 +20395,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20440,34 +20440,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20485,34 +20485,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20530,7 +20530,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20542,22 +20542,22 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>46.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20587,22 +20587,22 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20632,22 +20632,22 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20665,12 +20665,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -20687,12 +20687,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20722,22 +20722,22 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20755,34 +20755,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20812,22 +20812,22 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20857,12 +20857,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20902,12 +20902,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -21007,7 +21007,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21025,7 +21025,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21070,34 +21070,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Sudarshan Yellamaraju</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -21127,22 +21127,22 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -21172,22 +21172,22 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21217,22 +21217,22 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>70.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21262,17 +21262,17 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -21295,7 +21295,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -21307,22 +21307,22 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -21352,22 +21352,22 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21487,22 +21487,22 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18780,7 +18780,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-25</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -18820,24 +18820,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18882,17 +18882,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>64.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>55.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -18910,34 +18910,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -19000,34 +19000,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>62.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19062,17 +19062,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>62.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>55.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19107,17 +19107,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -19180,34 +19180,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>60.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19237,22 +19237,22 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19270,34 +19270,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>64.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19327,12 +19327,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19382,12 +19382,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Harry Hall</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19417,17 +19417,17 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>68.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19462,17 +19462,17 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19507,22 +19507,22 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19552,22 +19552,22 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19597,22 +19597,22 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>64.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19630,24 +19630,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19687,17 +19687,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19732,7 +19732,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -19742,12 +19742,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19777,22 +19777,22 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Gordon Sargent</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19822,22 +19822,22 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -20125,34 +20125,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>William Mouw</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20182,12 +20182,12 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20232,17 +20232,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20272,22 +20272,22 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20322,17 +20322,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20362,12 +20362,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>64.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20407,22 +20407,22 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20452,22 +20452,22 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20497,22 +20497,22 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,36 +18775,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-26</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18820,36 +18804,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18865,36 +18833,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18910,36 +18862,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18955,36 +18891,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19000,36 +18920,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19045,36 +18949,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19090,36 +18978,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-21</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19135,36 +19007,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19180,36 +19036,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19225,36 +19065,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19270,36 +19094,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19315,36 +19123,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19360,36 +19152,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19405,36 +19181,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Harry Hall</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19450,36 +19210,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19495,36 +19239,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19540,36 +19268,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19585,36 +19297,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19630,36 +19326,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19675,36 +19355,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19720,36 +19384,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19765,36 +19413,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19810,36 +19442,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gordon Sargent</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19855,36 +19471,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19900,36 +19500,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19945,36 +19529,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19990,36 +19558,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -20035,36 +19587,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -20080,36 +19616,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20125,36 +19645,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20170,36 +19674,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>William Mouw</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20215,36 +19703,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20260,36 +19732,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20305,36 +19761,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20350,36 +19790,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20395,36 +19819,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20440,36 +19848,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20485,36 +19877,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20530,36 +19906,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20575,36 +19935,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,36 +19964,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20665,36 +19993,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20710,36 +20022,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20755,36 +20051,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20800,36 +20080,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20845,36 +20109,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20890,36 +20138,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20935,36 +20167,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20980,36 +20196,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -21025,36 +20225,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -21070,36 +20254,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sudarshan Yellamaraju</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -21115,36 +20283,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -21160,36 +20312,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -21205,36 +20341,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21250,36 +20370,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21295,36 +20399,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21340,36 +20428,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21385,36 +20457,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21430,36 +20486,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21475,36 +20515,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21520,36 +20544,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21565,36 +20573,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21610,36 +20602,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21655,36 +20631,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jackson Koivun</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21700,36 +20660,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21745,36 +20689,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21790,36 +20718,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21835,36 +20747,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21880,36 +20776,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Marco Penge</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>
@@ -21925,26 +20805,18 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
@@ -21962,26 +20834,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -21991,36 +20855,6 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Max Greyserman</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>--</t>
@@ -22028,36 +20862,6 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Matt Wallace</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>--</t>
@@ -22065,36 +20869,6 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Paul Peterson</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>--</t>
@@ -22102,36 +20876,6 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Nick Hardy</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>--</t>
@@ -22139,36 +20883,6 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Maverick McNealy</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>--</t>
@@ -22176,36 +20890,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Jeffrey Kang</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>--</t>
@@ -22213,36 +20897,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Hank Lebioda</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>--</t>
@@ -22250,36 +20904,6 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tyler Duncan</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>--</t>
@@ -22287,36 +20911,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Cam Davis</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>--</t>
@@ -22324,36 +20918,6 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Joe Highsmith</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>--</t>
@@ -22361,36 +20925,6 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Christo Lamprecht</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>--</t>
@@ -22398,36 +20932,6 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tony Finau</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>--</t>
@@ -22435,36 +20939,6 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Kensei Hirata</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>--</t>
@@ -22472,36 +20946,6 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Hayden Springer</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>--</t>
@@ -22509,36 +20953,6 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Denny McCarthy</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>--</t>
@@ -22546,36 +20960,6 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Pierceson Coody</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>--</t>
@@ -22583,36 +20967,6 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Adam Schenk</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>--</t>
@@ -22620,36 +20974,6 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Peter Malnati</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>--</t>
@@ -22657,970 +20981,41 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Aaron Wise</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Jimmy Stanger</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ben Martin</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tom Hoge</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>David Skinns</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Aldrich Potgieter</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Andrew Putnam</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Michael Thompson</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Mac Meissner</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Will Gordon</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Rafael Campos</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Garrick Higgo</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Marcelo Rozo</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Isaiah Salinda</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Chandler Phillips</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Mackenzie Hughes</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Carson Lundell</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Bowen Mauss</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Pontus Nyholm</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Zach J. Johnson</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Rhett Rasmussen</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Davis Chatfield</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Rasmus Højgaard</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Boston Bracken</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Tyson Shelley</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Seonghyeon An</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>David Lingmerth</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Matt Snyder</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Rasmus Neergaard-Petersen</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Vince Whaley</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-    </row>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18693,7 +18693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.140625" bestFit="1" customWidth="1" style="37" min="1" max="1"/>
@@ -20987,35 +20987,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,17 +18775,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -18804,17 +18808,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -18833,17 +18841,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -18862,17 +18874,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -18891,17 +18907,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -18920,17 +18940,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -18949,17 +18973,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -18978,17 +19006,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -19007,17 +19039,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -19036,17 +19072,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -19065,17 +19105,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -19099,12 +19143,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -19123,17 +19171,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -19152,17 +19204,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -19181,17 +19237,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -19210,17 +19270,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -19239,17 +19303,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -19268,17 +19336,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -19297,17 +19369,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -19326,17 +19402,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -19355,17 +19435,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -19384,17 +19468,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -19413,17 +19501,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -19442,17 +19534,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -19471,17 +19567,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -19500,17 +19600,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -19529,17 +19633,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -19558,17 +19666,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -19587,17 +19699,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -19616,17 +19732,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -19645,17 +19765,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -19674,17 +19798,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -19703,17 +19831,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -19732,17 +19864,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -19761,17 +19897,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -19790,17 +19930,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -19819,17 +19963,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -19848,17 +19996,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -19877,17 +20029,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -19906,17 +20062,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -19935,17 +20095,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -19964,17 +20128,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -19993,17 +20161,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -20022,17 +20194,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -20051,7 +20227,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20061,7 +20237,11 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -20080,7 +20260,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20090,7 +20270,11 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -20109,7 +20293,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20119,7 +20303,11 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -20138,7 +20326,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20148,7 +20336,11 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -20167,7 +20359,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20177,7 +20369,11 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -20196,7 +20392,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20206,7 +20402,11 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -20225,7 +20425,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20235,7 +20435,11 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -20254,7 +20458,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20264,7 +20468,11 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -20283,7 +20491,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20293,7 +20501,11 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -20312,7 +20524,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20322,7 +20534,11 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -20341,7 +20557,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -20351,7 +20567,11 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -20370,17 +20590,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -20399,17 +20623,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -20428,17 +20656,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -20457,17 +20689,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -20486,17 +20722,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -20515,17 +20755,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -20544,17 +20788,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -20573,17 +20821,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -20602,17 +20854,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -20631,17 +20887,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -20660,17 +20920,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -20689,17 +20953,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -20718,17 +20986,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -20747,17 +21019,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -20776,17 +21052,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -20805,17 +21085,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -20834,17 +21118,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,19 +18775,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -18808,19 +18808,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -18841,19 +18841,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -18874,19 +18874,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -18907,19 +18907,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -18973,19 +18973,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -19006,19 +19006,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -19039,19 +19039,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -19072,19 +19072,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -19105,19 +19105,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -19138,19 +19138,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -19171,19 +19171,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -19204,19 +19204,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -19270,19 +19270,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -19303,19 +19303,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -19336,19 +19336,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -19369,19 +19369,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19402,19 +19402,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -19435,19 +19435,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -19468,19 +19468,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -19534,19 +19534,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -19567,19 +19567,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -19605,14 +19605,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -19633,19 +19633,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -19666,19 +19666,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,19 +19699,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,19 +19732,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -19765,19 +19765,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -19798,19 +19798,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -19831,19 +19831,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -19864,19 +19864,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -19897,19 +19897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19930,7 +19930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -19942,7 +19942,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19975,7 +19975,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20008,7 +20008,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -20029,7 +20029,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20041,7 +20041,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -20062,7 +20062,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20074,7 +20074,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -20095,7 +20095,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20107,7 +20107,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20140,7 +20140,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20173,7 +20173,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20206,7 +20206,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -20227,19 +20227,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20272,7 +20272,7 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20305,7 +20305,7 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -20326,7 +20326,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20338,7 +20338,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20371,7 +20371,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -20392,7 +20392,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20404,7 +20404,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20437,7 +20437,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -20458,19 +20458,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -20491,19 +20491,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -20524,19 +20524,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -20557,19 +20557,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -20590,7 +20590,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -20602,7 +20602,7 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -20623,7 +20623,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -20635,7 +20635,7 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -20656,7 +20656,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -20668,7 +20668,7 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -20701,7 +20701,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -20734,7 +20734,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -20755,7 +20755,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -20767,7 +20767,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -20788,19 +20788,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -20821,7 +20821,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -20833,7 +20833,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -20866,7 +20866,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -20887,19 +20887,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -20920,19 +20920,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -20998,7 +20998,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21031,7 +21031,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -21052,19 +21052,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -21085,19 +21085,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -21123,14 +21123,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,22 +18775,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -18808,22 +18812,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -18841,22 +18849,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
@@ -18874,22 +18886,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -18907,12 +18923,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -18922,7 +18938,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -18940,12 +18960,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -18955,7 +18975,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -18973,22 +18997,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -19006,22 +19034,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -19039,22 +19071,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -19072,22 +19108,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -19105,22 +19145,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -19138,22 +19182,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -19171,22 +19219,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -19204,22 +19256,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -19237,22 +19293,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -19270,22 +19330,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -19303,22 +19367,26 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -19336,22 +19404,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -19369,22 +19441,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -19402,22 +19478,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -19435,22 +19515,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -19468,22 +19552,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -19501,12 +19589,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -19516,7 +19604,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -19534,12 +19626,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -19549,7 +19641,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -19567,12 +19663,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -19582,7 +19678,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -19600,22 +19700,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -19633,22 +19737,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -19666,22 +19774,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -19699,22 +19811,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -19732,22 +19848,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -19765,22 +19885,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -19798,22 +19922,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -19831,22 +19959,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -19864,12 +19996,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -19879,7 +20011,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -19897,22 +20033,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -19930,22 +20070,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -19963,22 +20107,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
@@ -19996,12 +20144,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -20011,7 +20159,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -20029,12 +20181,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -20044,7 +20196,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -20062,12 +20218,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -20077,7 +20233,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -20095,22 +20255,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -20128,22 +20292,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -20161,22 +20329,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -20194,22 +20366,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -20227,22 +20403,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -20260,22 +20440,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -20293,22 +20477,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -20326,22 +20514,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -20359,22 +20551,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -20392,22 +20588,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -20425,12 +20625,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -20440,7 +20640,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -20458,22 +20662,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -20491,22 +20699,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -20524,22 +20736,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -20557,22 +20773,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -20590,22 +20810,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -20623,12 +20847,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -20638,7 +20862,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -20656,12 +20884,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -20671,7 +20899,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -20689,22 +20921,26 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -20722,22 +20958,26 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -20755,7 +20995,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -20767,10 +21007,14 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -20788,22 +21032,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -20821,7 +21069,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -20833,10 +21081,14 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -20854,7 +21106,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -20866,10 +21118,14 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -20887,22 +21143,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -20920,7 +21180,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -20935,7 +21195,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -20953,7 +21217,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -20965,10 +21229,14 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -20986,7 +21254,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -20998,10 +21266,14 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -21019,7 +21291,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21031,10 +21303,14 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -21052,22 +21328,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -21085,22 +21365,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
@@ -21133,7 +21417,11 @@
           <t>81.0</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18795,7 +18795,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -18832,7 +18836,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
@@ -18869,7 +18877,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -18906,7 +18918,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -18923,7 +18939,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18943,7 +18959,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
@@ -18960,7 +18980,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18980,7 +19000,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
@@ -18997,7 +19021,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19017,7 +19041,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -19034,7 +19062,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19054,7 +19082,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
@@ -19091,7 +19123,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -19108,7 +19144,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19125,10 +19161,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -19145,7 +19185,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19157,15 +19197,19 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -19182,7 +19226,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19194,15 +19238,19 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -19219,27 +19267,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -19256,7 +19308,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19268,15 +19320,19 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -19293,7 +19349,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19305,15 +19361,19 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
@@ -19330,7 +19390,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19347,10 +19407,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
@@ -19367,7 +19431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19379,15 +19443,19 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -19404,7 +19472,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19416,15 +19484,19 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
@@ -19441,7 +19513,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19453,15 +19525,19 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -19478,27 +19554,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -19515,27 +19595,31 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
@@ -19552,27 +19636,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -19589,27 +19677,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -19626,7 +19718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19638,15 +19730,19 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -19663,7 +19759,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19675,15 +19771,19 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -19700,12 +19800,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -19717,10 +19817,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -19737,27 +19841,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -19774,7 +19882,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19786,15 +19894,19 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -19811,7 +19923,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19823,15 +19935,19 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -19848,27 +19964,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -19890,7 +20010,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -19905,7 +20025,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -19922,27 +20046,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -19959,27 +20087,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -19996,27 +20128,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -20033,27 +20169,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -20070,19 +20210,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -20090,7 +20230,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -20107,7 +20251,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20119,15 +20263,19 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -20144,27 +20292,31 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -20181,7 +20333,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20193,15 +20345,19 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
@@ -20218,7 +20374,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20230,15 +20386,19 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
@@ -20255,7 +20415,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20267,15 +20427,19 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
@@ -20292,27 +20456,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
@@ -20329,27 +20497,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
@@ -20366,27 +20538,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
@@ -20403,27 +20579,31 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
@@ -20440,7 +20620,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20452,15 +20632,19 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
@@ -20477,7 +20661,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20489,15 +20673,19 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
@@ -20514,7 +20702,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20534,7 +20722,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -20551,7 +20743,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20571,7 +20763,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -20588,7 +20784,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20600,15 +20796,19 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -20645,7 +20845,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
@@ -20662,7 +20866,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20682,7 +20886,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
@@ -20699,27 +20907,31 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
@@ -20736,7 +20948,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20756,7 +20968,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
@@ -20773,7 +20989,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -20785,15 +21001,19 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
@@ -20810,7 +21030,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -20822,15 +21042,19 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
@@ -20847,7 +21071,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -20867,7 +21091,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
@@ -20884,7 +21112,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -20896,15 +21124,19 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
@@ -20921,7 +21153,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -20941,7 +21173,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
@@ -20958,12 +21194,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -20975,10 +21211,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
@@ -21015,7 +21255,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
@@ -21052,7 +21296,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -21089,7 +21337,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
@@ -21106,7 +21358,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21126,7 +21378,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
@@ -21143,7 +21399,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21163,7 +21419,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
@@ -21200,7 +21460,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
@@ -21237,7 +21501,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
@@ -21274,7 +21542,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
@@ -21311,7 +21583,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
@@ -21348,7 +21624,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
@@ -21385,7 +21665,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
@@ -21422,7 +21706,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,29 +18775,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18857,29 +18857,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -18898,12 +18898,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18915,12 +18915,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -18939,29 +18939,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -18980,29 +18980,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19021,12 +19021,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19062,19 +19062,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19103,29 +19103,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19144,29 +19144,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19185,29 +19185,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19226,29 +19226,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19267,29 +19267,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19308,29 +19308,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -19349,19 +19349,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -19390,19 +19390,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -19431,12 +19431,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19448,12 +19448,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -19472,29 +19472,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -19513,12 +19513,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -19554,29 +19554,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19595,29 +19595,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19648,17 +19648,17 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19689,17 +19689,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -19718,29 +19718,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -19759,29 +19759,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -19800,29 +19800,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -19841,29 +19841,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -19882,29 +19882,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -19923,29 +19923,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -19964,29 +19964,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -20005,29 +20005,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -20046,19 +20046,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -20087,29 +20087,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -20128,29 +20128,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -20169,29 +20169,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -20210,29 +20210,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -20251,29 +20251,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -20292,19 +20292,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -20333,29 +20333,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -20379,7 +20379,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -20415,29 +20415,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -20456,29 +20456,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -20497,29 +20497,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -20538,29 +20538,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -20579,29 +20579,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -20620,29 +20620,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -20661,29 +20661,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -20702,29 +20702,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -20743,29 +20743,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -20784,29 +20784,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20837,17 +20837,17 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20878,17 +20878,17 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>71.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -20907,29 +20907,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -20948,29 +20948,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -20989,29 +20989,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21042,17 +21042,17 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -21071,19 +21071,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -21112,29 +21112,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -21153,12 +21153,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -21170,12 +21170,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,12 +21194,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -21235,29 +21235,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,29 +21276,29 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>74.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,29 +21317,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,19 +21358,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,29 +21440,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,29 +21481,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,29 +21522,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>73.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,29 +21563,29 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21604,29 +21604,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -21657,17 +21657,17 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -21686,29 +21686,29 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,29 +18775,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18816,29 +18816,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18869,17 +18869,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -21165,17 +21165,17 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>74.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21211,12 +21211,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -21235,29 +21235,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -21288,17 +21288,17 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -21329,17 +21329,17 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,7 +21358,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21370,17 +21370,17 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21411,17 +21411,17 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21452,7 +21452,7 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -21462,7 +21462,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -21493,17 +21493,17 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,29 +21522,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21575,17 +21575,17 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>73.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -21645,29 +21645,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -21698,17 +21698,17 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18800,7 +18800,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18841,7 +18845,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18882,7 +18890,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18923,7 +18935,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18964,7 +18980,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19005,7 +19025,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19046,7 +19070,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19087,7 +19115,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19128,7 +19160,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19169,7 +19205,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19210,7 +19250,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19251,7 +19295,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19292,7 +19340,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19308,7 +19360,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19320,12 +19372,12 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -19333,7 +19385,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19349,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19361,20 +19417,24 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19415,7 +19475,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19456,7 +19520,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19497,7 +19565,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19538,7 +19610,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19579,7 +19655,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19620,7 +19700,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19636,7 +19720,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19648,20 +19732,24 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19677,7 +19765,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19689,7 +19777,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -19699,10 +19787,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19718,7 +19810,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19730,20 +19822,24 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19759,7 +19855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19771,7 +19867,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -19781,10 +19877,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19800,7 +19900,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19812,20 +19912,24 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19841,7 +19945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19853,20 +19957,24 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19882,7 +19990,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19894,20 +20002,24 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -19923,32 +20035,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -19964,32 +20080,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20005,7 +20125,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20017,20 +20137,24 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20046,7 +20170,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20058,20 +20182,24 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20087,7 +20215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20104,15 +20232,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20128,7 +20260,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20140,12 +20272,12 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -20153,7 +20285,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20169,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20186,15 +20322,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20210,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20227,15 +20367,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20251,7 +20395,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20263,20 +20407,24 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20292,7 +20440,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20304,12 +20452,12 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -20317,7 +20465,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20333,7 +20485,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20345,12 +20497,12 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -20358,7 +20510,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20374,7 +20530,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20386,20 +20542,24 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20415,7 +20575,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20427,20 +20587,24 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20456,7 +20620,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20468,20 +20632,24 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20497,32 +20665,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20538,7 +20710,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20555,15 +20727,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20579,7 +20755,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20591,20 +20767,24 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,32 +20800,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20686,7 +20870,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20727,7 +20915,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20768,7 +20960,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20809,7 +21005,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -20850,7 +21050,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -20866,7 +21070,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20878,12 +21082,12 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -20891,7 +21095,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -20907,7 +21115,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20919,12 +21127,12 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -20932,7 +21140,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -20948,7 +21160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20960,20 +21172,24 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -21014,7 +21230,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21055,7 +21275,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21096,7 +21320,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21137,7 +21365,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21178,7 +21410,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21219,7 +21455,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21260,7 +21500,11 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21301,7 +21545,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21342,7 +21590,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21383,7 +21635,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21424,7 +21680,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21465,7 +21725,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21506,7 +21770,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21547,7 +21815,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21588,7 +21860,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21629,7 +21905,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>
@@ -21670,7 +21950,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>--</t>
@@ -21711,7 +21995,11 @@
           <t>78.0</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>--</t>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,34 +18775,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -18865,34 +18865,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -18955,34 +18955,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -19000,34 +19000,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -19045,34 +19045,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -19090,34 +19090,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -19135,34 +19135,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -19180,34 +19180,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -19225,34 +19225,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19270,34 +19270,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -19315,34 +19315,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19360,34 +19360,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19405,34 +19405,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -19450,24 +19450,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -19495,12 +19495,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19512,7 +19512,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -19540,34 +19540,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -19585,26 +19585,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19630,34 +19630,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -19675,34 +19675,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -19720,19 +19720,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19765,12 +19765,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -19782,17 +19782,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19810,34 +19810,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19855,34 +19855,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19900,34 +19900,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19945,24 +19945,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19990,34 +19990,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -20035,34 +20035,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -20080,34 +20080,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20170,19 +20170,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Patrick Rodgers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -20192,12 +20192,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20215,34 +20215,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -20260,34 +20260,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -20305,34 +20305,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -20350,24 +20350,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20395,12 +20395,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20440,19 +20440,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -20462,12 +20462,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20485,34 +20485,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20530,34 +20530,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20575,34 +20575,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20620,34 +20620,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20665,34 +20665,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20710,34 +20710,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Jackson Suber</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20755,24 +20755,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20800,24 +20800,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20857,7 +20857,7 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -20867,12 +20867,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20902,22 +20902,22 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20947,22 +20947,22 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20992,7 +20992,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -21002,12 +21002,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21025,34 +21025,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21070,34 +21070,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21160,34 +21160,34 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21262,22 +21262,22 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -21295,19 +21295,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -21367,7 +21367,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21385,34 +21385,34 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21442,22 +21442,22 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -21475,7 +21475,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Kurt Kitayama</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21487,22 +21487,22 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -21520,12 +21520,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -21542,12 +21542,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -21565,34 +21565,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21622,22 +21622,22 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21667,22 +21667,22 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -21700,34 +21700,34 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -21745,34 +21745,34 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>Hiroshi Iwata</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -21790,34 +21790,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -21835,34 +21835,34 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -21975,7 +21975,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -21997,7 +21997,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,7 +18775,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Michael Brennan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -18787,22 +18787,22 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Keith Mitchell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18832,22 +18832,22 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -18865,34 +18865,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>Jacob Bridgeman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -18910,34 +18910,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Xander Schauffele</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -18955,34 +18955,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Brian Harman</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Ryan Gerard</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Jordan Smith</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19057,22 +19057,22 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>28.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Stephan Jaeger</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19102,22 +19102,22 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19147,22 +19147,22 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Min Woo Lee</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19192,7 +19192,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Sungjae Im</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19237,22 +19237,22 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -19270,34 +19270,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Zach Bauchou</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>42.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Jordan Spieth</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19327,22 +19327,22 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>36.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19372,22 +19372,22 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Max Homa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19417,22 +19417,22 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Adam Scott</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19462,22 +19462,22 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -19495,12 +19495,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Doug Ghim</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19512,17 +19512,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>26.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>Christiaan Bezuidenhout</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19552,7 +19552,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -19567,7 +19567,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19597,22 +19597,22 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>32.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -19630,19 +19630,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Michael Kim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -19652,12 +19652,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Billy Horschel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19687,22 +19687,22 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Hideki Matsuyama</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19732,22 +19732,22 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>38.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -19765,34 +19765,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Rasmus Neergaard-Petersen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -19810,12 +19810,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -19827,17 +19827,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>36.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19867,22 +19867,22 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Kosuke Sunagawa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19912,22 +19912,22 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Mac Meissner</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19957,22 +19957,22 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Justin Thomas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -20007,17 +20007,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -20035,12 +20035,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Tomohiro Ishizaka</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -20052,17 +20052,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -20080,34 +20080,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Ricky Castillo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>35.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20137,22 +20137,22 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>50.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20215,34 +20215,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Yoshinori Fujimoto</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>43.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -20260,34 +20260,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Johnny Keefer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>39.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -20305,12 +20305,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Collin Morikawa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Nico Echavarria</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>73.0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Yusaku Hosono</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20407,22 +20407,22 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20452,22 +20452,22 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Andrew Putnam</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20497,22 +20497,22 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -20530,34 +20530,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Michael Thorbjornsen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Jinichiro Kozuma</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20587,12 +20587,12 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Tony Finau</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20632,22 +20632,22 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -20665,24 +20665,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Nick Taylor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -20782,7 +20782,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -20800,34 +20800,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -20845,34 +20845,34 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Keegan Bradley</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>46.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -20890,12 +20890,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Beau Hossler</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -20907,17 +20907,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>47.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -20935,34 +20935,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Ryo Hisatsune</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -20980,34 +20980,34 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Matt McCarty</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -21025,34 +21025,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Keita Nakajima</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>38.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -21070,34 +21070,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Pierceson Coody</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -21115,12 +21115,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Matt Wallace</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -21132,17 +21132,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -21160,34 +21160,34 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Aguri Iwasaki</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -21205,24 +21205,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -21250,12 +21250,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -21272,12 +21272,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -21295,34 +21295,34 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -21340,34 +21340,34 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>David Lipsky</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>34.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -21385,34 +21385,34 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Maverick McNealy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>35.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -21430,12 +21430,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -21447,17 +21447,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -21502,7 +21502,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -21520,34 +21520,34 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -21565,34 +21565,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Alex Smalley</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -21610,34 +21610,34 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Wyndham Clark</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -21655,34 +21655,34 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Sanghee Lee</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>32.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -21700,12 +21700,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Steven Fisk</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -21717,17 +21717,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -21790,34 +21790,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Sahith Theegala</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -21835,34 +21835,34 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Koshin Nagasaki</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>73.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>30.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -21925,34 +21925,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Rickie Fowler</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>24.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18693,7 +18693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.140625" bestFit="1" customWidth="1" style="37" min="1" max="1"/>
@@ -18775,36 +18775,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Michael Brennan</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18820,36 +18804,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Keith Mitchell</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18865,36 +18833,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacob Bridgeman</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18910,36 +18862,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Xander Schauffele</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18955,36 +18891,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brian Harman</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19000,36 +18920,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Gerard</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19045,36 +18949,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Smith</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19090,36 +18978,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephan Jaeger</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19135,36 +19007,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19180,36 +19036,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Min Woo Lee</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19225,36 +19065,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sungjae Im</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19270,36 +19094,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zach Bauchou</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19315,36 +19123,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Spieth</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19360,36 +19152,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19405,36 +19181,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Max Homa</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19450,36 +19210,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Adam Scott</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19495,36 +19239,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Doug Ghim</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19540,36 +19268,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Christiaan Bezuidenhout</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19585,36 +19297,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19630,36 +19326,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Michael Kim</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19675,36 +19355,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Billy Horschel</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19720,36 +19384,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hideki Matsuyama</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19765,36 +19413,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rasmus Neergaard-Petersen</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19810,36 +19442,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19855,36 +19471,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19900,36 +19500,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kosuke Sunagawa</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19945,36 +19529,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mac Meissner</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19990,36 +19558,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Justin Thomas</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -20035,36 +19587,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tomohiro Ishizaka</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -20080,36 +19616,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ricky Castillo</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20125,36 +19645,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20170,36 +19674,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Patrick Rodgers</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20215,36 +19703,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yoshinori Fujimoto</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20260,36 +19732,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Johnny Keefer</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20305,36 +19761,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Collin Morikawa</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20350,36 +19790,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nico Echavarria</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20395,36 +19819,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yusaku Hosono</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20440,36 +19848,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20485,36 +19877,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Andrew Putnam</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20530,36 +19906,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Michael Thorbjornsen</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20575,36 +19935,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jinichiro Kozuma</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,36 +19964,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tony Finau</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20665,36 +19993,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nick Taylor</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20710,36 +20022,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jackson Suber</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20755,36 +20051,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20800,36 +20080,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20845,36 +20109,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Keegan Bradley</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20890,36 +20138,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Beau Hossler</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20935,36 +20167,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ryo Hisatsune</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20980,36 +20196,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Matt McCarty</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -21025,36 +20225,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Keita Nakajima</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -21070,36 +20254,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pierceson Coody</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -21115,36 +20283,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Matt Wallace</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -21160,36 +20312,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aguri Iwasaki</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -21205,36 +20341,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21250,36 +20370,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21295,36 +20399,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21340,36 +20428,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>David Lipsky</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21385,36 +20457,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maverick McNealy</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21430,36 +20486,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21475,36 +20515,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kurt Kitayama</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21520,36 +20544,20 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21565,36 +20573,20 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alex Smalley</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21610,36 +20602,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wyndham Clark</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21655,36 +20631,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sanghee Lee</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21700,36 +20660,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Steven Fisk</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21745,36 +20689,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hiroshi Iwata</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21790,36 +20718,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sahith Theegala</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21835,36 +20747,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Koshin Nagasaki</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21880,36 +20776,20 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>
@@ -21925,36 +20805,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rickie Fowler</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>--</t>
@@ -21970,36 +20834,20 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>--</t>
@@ -22007,6 +20855,28 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Bill Haas</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>--</t>
@@ -22014,6 +20884,28 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Corey Conners</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>--</t>
@@ -22021,6 +20913,28 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Taylor Pendrith</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>--</t>
@@ -22028,6 +20942,28 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Davis Riley</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>--</t>
@@ -22035,6 +20971,28 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Andrew Novak</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>--</t>
@@ -22042,6 +21000,28 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Aldrich Potgieter</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>--</t>
@@ -22049,6 +21029,28 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Charley Hoffman</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>--</t>
@@ -22056,6 +21058,28 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chris Kirk</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>--</t>
@@ -22063,6 +21087,28 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Henrik Norlander</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>--</t>
@@ -22070,6 +21116,28 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mark Hubbard</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>--</t>
@@ -22077,6 +21145,28 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Aaron Wise</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>--</t>
@@ -22084,6 +21174,28 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dylan Wu</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>--</t>
@@ -22091,6 +21203,28 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ryan Brehm</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>--</t>
@@ -22098,6 +21232,28 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Patton Kizzire</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>--</t>
@@ -22105,6 +21261,28 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Peter Malnati</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>--</t>
@@ -22112,6 +21290,28 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Adam Long</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>--</t>
@@ -22119,6 +21319,28 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Max McGreevy</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>--</t>
@@ -22126,6 +21348,28 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nick Dunlap</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>--</t>
@@ -22133,11 +21377,729 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Rafael Campos</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ben Martin</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Austin Cook</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Nick Hardy</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Denny McCarthy</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Kristoffer Ventura</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Max Greyserman</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hank Lebioda</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>A.J. Ewart</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ben James</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>David Ford</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Miles Russell</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Paul Peterson</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Patrick Fishburn</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>John VanDerLaan</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kensei Hirata</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Nick Jones</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mason Howell</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Trace Crowe</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Alejandro Tosti</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pontus Nyholm</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chandler Blanchet</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ren Yonezawa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jay Leng</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Jimmy Stanger</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jeffrey Kang</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Isaiah Salinda</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Greg Koch</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Adrien Dumont de Chassart</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Virgilio Paz</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,17 +18775,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -18804,17 +18808,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -18833,17 +18841,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -18862,17 +18874,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -18891,17 +18907,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -18925,12 +18945,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -18949,17 +18973,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -18978,17 +19006,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -19007,17 +19039,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -19036,17 +19072,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -19065,17 +19105,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -19099,12 +19143,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -19123,17 +19171,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -19152,17 +19204,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -19181,17 +19237,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -19210,17 +19270,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -19239,17 +19303,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -19268,17 +19336,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -19297,17 +19369,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -19326,17 +19402,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -19355,17 +19435,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -19384,17 +19468,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -19413,17 +19501,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -19442,17 +19534,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -19471,17 +19567,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -19500,17 +19600,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -19529,17 +19633,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -19558,17 +19666,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -19587,17 +19699,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -19616,17 +19732,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -19645,17 +19765,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -19674,17 +19798,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -19703,17 +19831,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -19732,17 +19864,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -19761,17 +19897,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -19790,17 +19930,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -19819,7 +19963,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19829,7 +19973,11 @@
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -19848,7 +19996,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -19858,7 +20006,11 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -19877,7 +20029,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -19887,7 +20039,11 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -19906,7 +20062,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -19916,7 +20072,11 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -19935,7 +20095,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -19945,7 +20105,11 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -19964,7 +20128,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -19974,7 +20138,11 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -19993,7 +20161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20003,7 +20171,11 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -20022,7 +20194,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20032,7 +20204,11 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -20051,7 +20227,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20061,7 +20237,11 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -20080,7 +20260,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20090,7 +20270,11 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -20109,17 +20293,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -20138,17 +20326,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -20167,17 +20359,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -20196,17 +20392,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -20225,17 +20425,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -20254,17 +20458,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -20283,17 +20491,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -20312,17 +20524,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -20341,17 +20557,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -20370,17 +20590,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -20399,17 +20623,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -20428,17 +20656,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -20457,17 +20689,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -20486,17 +20722,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -20525,7 +20765,11 @@
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -20554,7 +20798,11 @@
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -20583,7 +20831,11 @@
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -20612,7 +20864,11 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -20641,7 +20897,11 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -20670,7 +20930,11 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -20699,7 +20963,11 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -20728,7 +20996,11 @@
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -20757,7 +21029,11 @@
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -20786,7 +21062,11 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -20815,7 +21095,11 @@
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -20844,7 +21128,11 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -20873,7 +21161,11 @@
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -20902,7 +21194,11 @@
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -20931,7 +21227,11 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -20960,7 +21260,11 @@
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -20989,7 +21293,11 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -21018,7 +21326,11 @@
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -21047,7 +21359,11 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -21076,7 +21392,11 @@
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
@@ -21105,7 +21425,11 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -21134,7 +21458,11 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
@@ -21163,7 +21491,11 @@
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -21192,7 +21524,11 @@
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
@@ -21221,7 +21557,11 @@
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -21250,7 +21590,11 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -21279,7 +21623,11 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -21308,7 +21656,11 @@
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -21337,7 +21689,11 @@
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
@@ -21366,7 +21722,11 @@
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
@@ -21395,7 +21755,11 @@
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
@@ -21424,7 +21788,11 @@
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -21448,7 +21816,11 @@
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
@@ -21472,7 +21844,11 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
@@ -21496,7 +21872,11 @@
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
@@ -21520,7 +21900,11 @@
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -21544,7 +21928,11 @@
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -21568,7 +21956,11 @@
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -21592,7 +21984,11 @@
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
@@ -21616,7 +22012,11 @@
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -21640,7 +22040,11 @@
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -21664,7 +22068,11 @@
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -21688,7 +22096,11 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -21712,7 +22124,11 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -21736,7 +22152,11 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -21760,7 +22180,11 @@
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -21784,7 +22208,11 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -21808,7 +22236,11 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -21832,7 +22264,11 @@
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -21856,7 +22292,11 @@
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -21880,7 +22320,11 @@
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
@@ -21904,7 +22348,11 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
@@ -21928,7 +22376,11 @@
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -21952,7 +22404,11 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
@@ -21976,7 +22432,11 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
@@ -22000,7 +22460,11 @@
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
@@ -22024,7 +22488,11 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -22048,7 +22516,11 @@
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -22072,7 +22544,11 @@
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -22096,7 +22572,11 @@
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,19 +18775,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -18808,19 +18808,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -18841,19 +18841,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -18874,19 +18874,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -18912,14 +18912,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -18973,19 +18973,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -19006,19 +19006,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -19039,19 +19039,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -19072,19 +19072,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -19105,19 +19105,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -19143,14 +19143,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -19171,19 +19171,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -19204,19 +19204,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -19270,19 +19270,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -19303,19 +19303,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -19336,19 +19336,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -19369,19 +19369,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19402,19 +19402,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -19435,19 +19435,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -19468,19 +19468,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -19534,19 +19534,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -19567,19 +19567,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -19600,19 +19600,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -19633,12 +19633,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -19666,19 +19666,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,19 +19699,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,19 +19732,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -19765,19 +19765,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -19798,19 +19798,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -19831,19 +19831,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -19864,19 +19864,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -19897,19 +19897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19930,19 +19930,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -19963,19 +19963,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19996,19 +19996,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -20029,19 +20029,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -20062,12 +20062,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -20095,19 +20095,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -20128,19 +20128,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -20161,19 +20161,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20194,19 +20194,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -20227,19 +20227,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -20260,19 +20260,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -20293,19 +20293,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -20326,19 +20326,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -20359,19 +20359,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -20392,19 +20392,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -20425,19 +20425,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -20458,19 +20458,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -20491,19 +20491,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -20524,19 +20524,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -20557,19 +20557,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -20590,19 +20590,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -20623,19 +20623,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -20656,19 +20656,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -20689,19 +20689,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -20722,19 +20722,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -20755,19 +20755,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -20788,19 +20788,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -20821,19 +20821,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -20854,19 +20854,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -20887,19 +20887,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -20920,19 +20920,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chez Reavie</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -20986,19 +20986,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -21019,19 +21019,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Bill Haas</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -21052,19 +21052,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -21085,19 +21085,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -21118,19 +21118,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -21151,19 +21151,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bill Haas</t>
+          <t>Mason Howell</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -21184,19 +21184,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -21217,19 +21217,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -21250,19 +21250,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -21283,19 +21283,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Greg Koch</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -21316,19 +21316,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21361,7 +21361,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21394,7 +21394,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -21427,7 +21427,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -21460,7 +21460,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -21493,7 +21493,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21526,7 +21526,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ryan Brehm</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -21559,7 +21559,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -21580,7 +21580,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21592,7 +21592,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -21625,7 +21625,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -21658,7 +21658,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -21679,7 +21679,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21691,7 +21691,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -21712,7 +21712,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21724,7 +21724,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21757,7 +21757,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21790,7 +21790,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin Cook</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21818,7 +21818,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21874,7 +21874,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21902,7 +21902,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Jay Leng</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21930,7 +21930,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -21958,7 +21958,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -21986,7 +21986,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22014,7 +22014,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22042,7 +22042,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -22058,19 +22058,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -22086,19 +22086,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -22114,19 +22114,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -22142,19 +22142,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -22170,19 +22170,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -22198,19 +22198,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nick Jones</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -22226,19 +22226,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mason Howell</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -22254,19 +22254,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Austin Cook</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -22282,19 +22282,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Nick Jones</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -22310,19 +22310,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -22338,19 +22338,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -22366,19 +22366,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -22394,19 +22394,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jay Leng</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -22422,19 +22422,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -22450,19 +22450,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Ryan Brehm</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -22478,19 +22478,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -22506,19 +22506,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Greg Koch</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -22534,19 +22534,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Virgilio Paz</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -22562,19 +22562,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Virgilio Paz</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,19 +18775,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -18808,7 +18808,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18874,19 +18874,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -18907,19 +18907,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18973,19 +18973,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -19006,19 +19006,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -19039,19 +19039,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -19072,19 +19072,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19138,19 +19138,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -19171,19 +19171,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -19204,19 +19204,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -19237,19 +19237,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -19270,19 +19270,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -19303,19 +19303,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -19336,19 +19336,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -19369,19 +19369,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19402,19 +19402,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -19435,19 +19435,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -19468,19 +19468,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -19534,19 +19534,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -19567,19 +19567,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -19600,19 +19600,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -19633,19 +19633,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -19666,19 +19666,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,7 +19699,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19711,7 +19711,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19744,7 +19744,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -19765,19 +19765,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -19798,19 +19798,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -19831,19 +19831,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -19864,19 +19864,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -19897,19 +19897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -19930,19 +19930,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -19963,19 +19963,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -19996,19 +19996,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -20029,19 +20029,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -20062,19 +20062,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -20095,19 +20095,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -20128,19 +20128,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -20161,19 +20161,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20194,19 +20194,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -20227,19 +20227,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -20260,19 +20260,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -20293,19 +20293,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -20326,19 +20326,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -20359,19 +20359,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -20392,19 +20392,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -20425,19 +20425,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -20458,19 +20458,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -20491,19 +20491,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -20529,14 +20529,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -20557,19 +20557,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -20590,19 +20590,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -20623,19 +20623,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -20656,19 +20656,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -20689,19 +20689,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -20722,19 +20722,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -20755,19 +20755,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -20788,19 +20788,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -20821,19 +20821,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -20854,19 +20854,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -20887,19 +20887,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -20920,19 +20920,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -20953,19 +20953,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -20986,19 +20986,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -21024,14 +21024,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -21052,19 +21052,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -21085,19 +21085,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -21118,19 +21118,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -21151,19 +21151,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mason Howell</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21196,7 +21196,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21229,7 +21229,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21262,7 +21262,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -21283,7 +21283,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greg Koch</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21295,7 +21295,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21328,7 +21328,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -21349,19 +21349,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -21382,19 +21382,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -21415,19 +21415,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -21448,19 +21448,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -21481,19 +21481,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -21514,19 +21514,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -21547,19 +21547,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -21580,19 +21580,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -21613,19 +21613,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -21646,19 +21646,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -21679,19 +21679,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -21712,19 +21712,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -21745,19 +21745,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -21778,19 +21778,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -21806,19 +21806,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -21834,7 +21834,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21874,7 +21874,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21902,7 +21902,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jay Leng</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21930,7 +21930,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21958,7 +21958,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21986,7 +21986,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22014,7 +22014,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22042,7 +22042,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -22058,19 +22058,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Austin Cook</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -22086,19 +22086,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -22114,19 +22114,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Jay Leng</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -22142,19 +22142,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Greg Koch</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -22182,7 +22182,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -22198,7 +22198,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22238,7 +22238,7 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -22254,7 +22254,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin Cook</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22266,7 +22266,7 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -22282,7 +22282,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nick Jones</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22294,7 +22294,7 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Nick Jones</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22322,7 +22322,7 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Mason Howell</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22350,7 +22350,7 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22434,7 +22434,7 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -22478,19 +22478,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -22506,7 +22506,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chez Reavie</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -22518,7 +22518,7 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -22534,19 +22534,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Virgilio Paz</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -22562,19 +22562,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Virgilio Paz</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18787,7 +18787,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -19381,7 +19381,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -19678,7 +19678,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -19699,19 +19699,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20173,7 +20173,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -20701,7 +20701,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -21184,19 +21184,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -21217,19 +21217,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -21580,7 +21580,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21724,7 +21724,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21757,7 +21757,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21790,7 +21790,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -21806,7 +21806,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21818,7 +21818,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -22126,7 +22126,7 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -22154,7 +22154,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -22574,7 +22574,7 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18780,7 +18780,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18790,7 +18790,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -18808,22 +18812,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -18841,22 +18849,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
@@ -18874,12 +18886,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18889,7 +18901,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -18907,22 +18923,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -18940,22 +18960,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -18973,12 +18997,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -18988,7 +19012,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -19006,22 +19034,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -19039,22 +19071,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -19072,22 +19108,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -19105,22 +19145,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -19138,22 +19182,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -19171,22 +19219,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -19204,22 +19256,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -19237,22 +19293,26 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -19270,22 +19330,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -19303,22 +19367,26 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -19336,22 +19404,26 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -19369,7 +19441,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19381,10 +19453,14 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -19402,22 +19478,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -19435,22 +19515,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -19468,22 +19552,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -19501,22 +19589,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -19534,22 +19626,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -19567,12 +19663,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -19582,7 +19678,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -19600,22 +19700,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -19633,22 +19737,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -19666,22 +19774,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -19699,22 +19811,26 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -19732,22 +19848,26 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -19765,12 +19885,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -19780,7 +19900,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -19798,12 +19922,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -19813,7 +19937,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -19831,22 +19959,26 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -19864,22 +19996,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -19897,12 +20033,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -19912,7 +20048,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -19930,22 +20070,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -19963,22 +20107,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
@@ -19996,22 +20144,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -20029,22 +20181,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -20062,22 +20218,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -20095,22 +20255,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -20128,22 +20292,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -20161,22 +20329,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -20194,22 +20366,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -20227,22 +20403,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -20260,22 +20440,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -20293,22 +20477,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -20326,22 +20514,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -20359,22 +20551,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -20392,22 +20588,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -20425,12 +20625,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -20440,7 +20640,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -20458,22 +20662,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -20491,22 +20699,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -20524,22 +20736,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -20557,22 +20773,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -20590,22 +20810,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -20623,22 +20847,26 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -20656,22 +20884,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -20689,22 +20921,26 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -20722,22 +20958,26 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
@@ -20755,12 +20995,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Bill Haas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -20770,7 +21010,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -20788,22 +21032,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -20821,22 +21069,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -20854,22 +21106,26 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -20887,22 +21143,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -20920,22 +21180,26 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -20953,22 +21217,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -20986,22 +21254,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -21019,22 +21291,26 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bill Haas</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -21052,22 +21328,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -21085,22 +21365,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
@@ -21118,7 +21402,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -21130,10 +21414,14 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -21151,7 +21439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -21163,10 +21451,14 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>46.0</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
@@ -21184,7 +21476,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21196,10 +21488,14 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -21217,7 +21513,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21232,7 +21528,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -21250,22 +21550,26 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -21283,22 +21587,26 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -21316,22 +21624,26 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -21349,22 +21661,26 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -21382,22 +21698,26 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -21415,22 +21735,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -21448,22 +21772,26 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -21481,7 +21809,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -21493,10 +21821,14 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -21514,7 +21846,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21529,7 +21861,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -21547,7 +21883,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -21562,7 +21898,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -21580,7 +21920,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21595,7 +21935,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -21613,7 +21957,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -21628,7 +21972,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -21646,7 +21994,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -21661,7 +22009,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -21679,7 +22031,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21694,7 +22046,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -21712,7 +22068,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -21727,7 +22083,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -21745,7 +22105,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21760,7 +22120,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -21778,7 +22142,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21793,7 +22157,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
     </row>
@@ -21806,7 +22174,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -21821,7 +22189,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
     </row>
@@ -21834,7 +22206,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Austin Cook</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21849,7 +22221,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
     </row>
@@ -21862,7 +22238,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -21874,10 +22250,14 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
     </row>
@@ -21890,7 +22270,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21902,10 +22282,14 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
     </row>
@@ -21918,7 +22302,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Mason Howell</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21930,10 +22314,14 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
     </row>
@@ -21946,7 +22334,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Nick Jones</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -21958,10 +22346,14 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
     </row>
@@ -21974,7 +22366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Jay Leng</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -21989,7 +22381,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
     </row>
@@ -22002,7 +22398,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22017,7 +22413,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
     </row>
@@ -22030,7 +22430,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22045,7 +22445,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
     </row>
@@ -22058,7 +22462,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin Cook</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22073,7 +22477,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
     </row>
@@ -22086,7 +22494,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -22101,7 +22509,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
     </row>
@@ -22114,7 +22526,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jay Leng</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22129,7 +22541,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
     </row>
@@ -22142,7 +22558,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Greg Koch</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22157,7 +22573,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
     </row>
@@ -22170,7 +22590,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -22182,10 +22602,14 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
     </row>
@@ -22198,7 +22622,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -22210,10 +22634,14 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
     </row>
@@ -22226,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22241,7 +22669,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
     </row>
@@ -22254,7 +22686,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22269,7 +22701,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
     </row>
@@ -22282,7 +22718,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22297,7 +22733,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
     </row>
@@ -22310,7 +22750,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nick Jones</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22325,7 +22765,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
     </row>
@@ -22338,22 +22782,26 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mason Howell</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
     </row>
@@ -22366,7 +22814,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22381,7 +22829,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
     </row>
@@ -22394,22 +22846,26 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>Greg Koch</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
     </row>
@@ -22422,22 +22878,26 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chez Reavie</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
     </row>
@@ -22450,12 +22910,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ryan Brehm</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -22465,7 +22925,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
     </row>
@@ -22478,22 +22942,26 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
     </row>
@@ -22506,22 +22974,26 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
     </row>
@@ -22534,22 +23006,26 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Ryan Brehm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
     </row>
@@ -22567,7 +23043,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -22577,7 +23053,11 @@
           <t>78.0</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
     </row>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,24 +18775,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -18812,24 +18812,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18866,7 +18866,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -18923,24 +18923,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -18960,24 +18960,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -18997,24 +18997,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>64.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>49.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -19034,24 +19034,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -19071,24 +19071,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -19108,24 +19108,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -19162,7 +19162,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -19182,24 +19182,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -19219,24 +19219,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -19256,24 +19256,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -19293,24 +19293,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>37.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -19330,24 +19330,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -19367,12 +19367,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -19404,12 +19404,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -19441,24 +19441,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -19478,24 +19478,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>55.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -19515,24 +19515,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>51.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -19552,24 +19552,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -19589,24 +19589,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -19626,24 +19626,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -19663,24 +19663,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -19700,24 +19700,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -19737,24 +19737,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -19774,24 +19774,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -19811,24 +19811,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -19848,24 +19848,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -19885,24 +19885,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>54.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -19922,12 +19922,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -19939,7 +19939,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -19959,24 +19959,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -19996,24 +19996,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -20033,24 +20033,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -20070,24 +20070,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -20107,24 +20107,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -20144,24 +20144,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -20181,24 +20181,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -20218,12 +20218,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -20255,24 +20255,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -20292,24 +20292,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -20329,12 +20329,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -20366,24 +20366,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -20403,24 +20403,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -20440,24 +20440,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -20477,24 +20477,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -20514,24 +20514,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -20551,24 +20551,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -20588,24 +20588,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -20625,24 +20625,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -20662,24 +20662,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -20699,24 +20699,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -20736,24 +20736,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -20773,24 +20773,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -20810,12 +20810,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -20827,7 +20827,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -20847,24 +20847,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -20884,24 +20884,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -20921,24 +20921,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -20958,24 +20958,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -20995,24 +20995,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bill Haas</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -21032,12 +21032,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -21069,24 +21069,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -21106,24 +21106,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -21143,24 +21143,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -21180,24 +21180,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -21217,24 +21217,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -21254,12 +21254,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -21291,12 +21291,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -21328,24 +21328,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -21365,24 +21365,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -21402,24 +21402,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -21439,24 +21439,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -21476,24 +21476,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -21513,24 +21513,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -21550,24 +21550,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -21587,24 +21587,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -21624,24 +21624,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -21661,12 +21661,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Bill Haas</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -21698,12 +21698,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -21735,24 +21735,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -21772,24 +21772,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -21809,24 +21809,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -21846,19 +21846,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -21883,24 +21883,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -21920,24 +21920,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>Mason Howell</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -21957,24 +21957,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Austin Cook</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -21994,12 +21994,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -22011,7 +22011,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -22031,24 +22031,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -22068,12 +22068,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -22105,12 +22105,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -22122,7 +22122,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -22142,12 +22142,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -22159,7 +22159,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -22191,7 +22191,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -22206,24 +22206,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin Cook</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -22238,12 +22238,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -22270,24 +22270,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mason Howell</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -22314,12 +22314,12 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -22366,7 +22366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jay Leng</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22378,12 +22378,12 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -22410,12 +22410,12 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22442,12 +22442,12 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -22462,7 +22462,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22474,12 +22474,12 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -22506,12 +22506,12 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22570,12 +22570,12 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -22590,24 +22590,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chez Reavie</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -22622,7 +22622,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -22634,12 +22634,12 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22666,12 +22666,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22698,12 +22698,12 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -22718,24 +22718,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -22750,24 +22750,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -22782,24 +22782,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Jay Leng</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -22814,24 +22814,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>Greg Koch</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -22846,24 +22846,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Greg Koch</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -22878,24 +22878,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -22910,24 +22910,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Max Greyserman</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -22942,24 +22942,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -22974,24 +22974,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Ryan Brehm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -23006,24 +23006,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ryan Brehm</t>
+          <t>Virgilio Paz</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>73.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -23038,24 +23038,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Virgilio Paz</t>
+          <t>Max Greyserman</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18886,7 +18886,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18898,12 +18898,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -18960,24 +18960,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -18997,24 +18997,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>64.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19046,12 +19046,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -19071,12 +19071,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -19108,24 +19108,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -19145,24 +19145,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -19182,24 +19182,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>65.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19231,12 +19231,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19268,12 +19268,12 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19305,12 +19305,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19342,12 +19342,12 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -19367,7 +19367,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19379,12 +19379,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19416,12 +19416,12 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19453,12 +19453,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -19478,24 +19478,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -19515,24 +19515,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>65.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -19552,24 +19552,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19601,12 +19601,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19638,12 +19638,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19675,12 +19675,12 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>38.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19712,12 +19712,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -19737,24 +19737,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -19774,24 +19774,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -19811,24 +19811,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -19848,24 +19848,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -19885,24 +19885,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -19922,24 +19922,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -19959,24 +19959,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20008,12 +20008,12 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20045,12 +20045,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>65.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>38.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -20070,7 +20070,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20082,12 +20082,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -20107,24 +20107,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -20144,19 +20144,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -20181,19 +20181,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -20218,24 +20218,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -20255,19 +20255,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -20292,19 +20292,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -20329,19 +20329,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -20366,19 +20366,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20415,12 +20415,12 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chandler Phillips</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20452,12 +20452,12 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20489,12 +20489,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -20551,7 +20551,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20568,7 +20568,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -20588,7 +20588,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20600,12 +20600,12 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -20625,7 +20625,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -20637,12 +20637,12 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20674,12 +20674,12 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -20699,7 +20699,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20711,12 +20711,12 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -20736,24 +20736,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -20773,19 +20773,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -20810,12 +20810,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -20827,7 +20827,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -20847,24 +20847,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -20884,24 +20884,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -20921,24 +20921,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>28.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -20958,24 +20958,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -20995,24 +20995,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -21032,24 +21032,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Matthew Anderson</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -21081,12 +21081,12 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21118,12 +21118,12 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21155,12 +21155,12 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -21180,12 +21180,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charley Hoffman</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -21217,19 +21217,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jimmy Stanger</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -21254,12 +21254,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Taylor Pendrith</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -21291,12 +21291,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Patrick Fishburn</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -21328,24 +21328,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Justin Lower</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -21365,24 +21365,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alejandro Tosti</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -21402,24 +21402,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>48.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Tyler Duncan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -21451,12 +21451,12 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -21476,7 +21476,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Charley Hoffman</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21488,12 +21488,12 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -21513,7 +21513,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Taylor Montgomery</t>
+          <t>Jimmy Stanger</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21525,12 +21525,12 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -21550,19 +21550,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Will Gordon</t>
+          <t>Cameron Champ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -21587,24 +21587,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>John VanDerLaan</t>
+          <t>Marcelo Rozo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -21624,24 +21624,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aaron Wise</t>
+          <t>Taylor Pendrith</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -21661,19 +21661,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bill Haas</t>
+          <t>Patrick Fishburn</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -21698,24 +21698,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Camilo Villegas</t>
+          <t>Matthew Anderson</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -21735,12 +21735,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Justin Lower</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -21772,24 +21772,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tyler Duncan</t>
+          <t>Chandler Phillips</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>71.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>32.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -21809,24 +21809,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Alejandro Tosti</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Will Gordon</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21858,12 +21858,12 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Marcelo Rozo</t>
+          <t>John VanDerLaan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -21895,12 +21895,12 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -21920,24 +21920,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mason Howell</t>
+          <t>Aaron Wise</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -21957,19 +21957,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin Cook</t>
+          <t>David Lingmerth</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -21994,12 +21994,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Patton Kizzire</t>
+          <t>John Parry</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -22011,7 +22011,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -22031,12 +22031,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pontus Nyholm</t>
+          <t>Bill Haas</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -22048,7 +22048,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -22068,24 +22068,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cameron Champ</t>
+          <t>Camilo Villegas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>54.0</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -22105,24 +22105,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>John Parry</t>
+          <t>Haotong Li</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -22142,24 +22142,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Taylor Montgomery</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -22174,24 +22174,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ben James</t>
+          <t>Mason Howell</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -22206,24 +22206,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>David Lingmerth</t>
+          <t>C.T. Pan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -22238,24 +22238,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Austin Cook</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -22270,24 +22270,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Luke List</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -22302,24 +22302,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chez Reavie</t>
+          <t>Patton Kizzire</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -22334,19 +22334,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nick Jones</t>
+          <t>Christo Lamprecht</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -22366,24 +22366,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Adam Long</t>
+          <t>Pontus Nyholm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -22398,24 +22398,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Harry Higgs</t>
+          <t>Kevin Streelman</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -22430,24 +22430,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kevin Yu</t>
+          <t>Troy Merritt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -22462,24 +22462,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Aaron Baddeley</t>
+          <t>Ben James</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>C.T. Pan</t>
+          <t>Chez Reavie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -22506,12 +22506,12 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Luke List</t>
+          <t>Nick Jones</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22538,12 +22538,12 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -22558,7 +22558,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Christo Lamprecht</t>
+          <t>Adam Long</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -22590,24 +22590,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Haotong Li</t>
+          <t>Matthieu Pavon</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -22622,24 +22622,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kevin Streelman</t>
+          <t>Adam Schenk</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -22654,24 +22654,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Troy Merritt</t>
+          <t>Kevin Yu</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -22686,24 +22686,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>William McGirt</t>
+          <t>Harry Higgs</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -22718,7 +22718,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Matthieu Pavon</t>
+          <t>Aaron Baddeley</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22730,12 +22730,12 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -22750,12 +22750,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nixon Lauritzen</t>
+          <t>Jay Leng</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jay Leng</t>
+          <t>William McGirt</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22814,12 +22814,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greg Koch</t>
+          <t>Nixon Lauritzen</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Adam Schenk</t>
+          <t>Austin Lemieux</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -22858,12 +22858,12 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -22878,24 +22878,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Aldrich Potgieter</t>
+          <t>Greg Koch</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin Lemieux</t>
+          <t>Aldrich Potgieter</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -22922,12 +22922,12 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -22942,24 +22942,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Camiko Smith</t>
+          <t>Ryan Brehm</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -22974,24 +22974,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ryan Brehm</t>
+          <t>Virgilio Paz</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
           <t>73.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>76.0</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -23006,24 +23006,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Virgilio Paz</t>
+          <t>Camiko Smith</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18795,7 +18795,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
@@ -18832,7 +18836,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
@@ -18869,7 +18877,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
@@ -18906,7 +18918,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -18923,7 +18939,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18943,7 +18959,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
@@ -18980,7 +19000,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
@@ -18997,7 +19021,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19017,7 +19041,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -19054,7 +19082,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
@@ -19071,7 +19103,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19091,7 +19123,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -19108,7 +19144,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19128,7 +19164,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -19165,7 +19205,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -19202,7 +19246,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
@@ -19239,7 +19287,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
@@ -19276,7 +19328,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -19313,7 +19369,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
@@ -19330,7 +19390,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19350,7 +19410,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
@@ -19387,7 +19451,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -19404,7 +19472,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19424,7 +19492,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
@@ -19441,7 +19513,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19461,7 +19533,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
@@ -19478,7 +19554,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19498,7 +19574,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
@@ -19515,7 +19595,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19535,7 +19615,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
@@ -19552,7 +19636,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19572,7 +19656,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
@@ -19589,7 +19677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19601,7 +19689,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -19609,7 +19697,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
@@ -19626,7 +19718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19638,15 +19730,19 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
@@ -19663,7 +19759,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19675,15 +19771,19 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
@@ -19700,7 +19800,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19720,7 +19820,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
@@ -19737,7 +19841,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19749,15 +19853,19 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
@@ -19774,7 +19882,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19786,15 +19894,19 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
@@ -19811,7 +19923,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19823,15 +19935,19 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
@@ -19848,7 +19964,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19860,15 +19976,19 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
@@ -19885,7 +20005,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19897,15 +20017,19 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -19922,7 +20046,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19934,15 +20058,19 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -19959,7 +20087,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19971,15 +20099,19 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
@@ -19996,27 +20128,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
@@ -20033,27 +20169,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -20070,7 +20210,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20082,15 +20222,19 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
@@ -20107,7 +20251,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20127,7 +20271,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
@@ -20144,7 +20292,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20164,7 +20312,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
@@ -20181,7 +20333,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20193,15 +20345,19 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
@@ -20238,7 +20394,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
@@ -20275,7 +20435,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
@@ -20292,7 +20456,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20304,15 +20468,19 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
@@ -20329,7 +20497,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20341,15 +20509,19 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
@@ -20386,7 +20558,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
@@ -20423,7 +20599,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
@@ -20460,7 +20640,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
@@ -20497,7 +20681,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
@@ -20534,7 +20722,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
@@ -20571,7 +20763,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
@@ -20608,7 +20804,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
@@ -20645,7 +20845,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
@@ -20682,7 +20886,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
@@ -20719,7 +20927,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
@@ -20756,7 +20968,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
@@ -20793,7 +21009,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
@@ -20830,7 +21050,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
@@ -20867,7 +21091,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
@@ -20904,7 +21132,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
@@ -20941,7 +21173,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
@@ -20978,7 +21214,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
@@ -21015,7 +21255,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
@@ -21052,7 +21296,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
@@ -21089,7 +21337,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
@@ -21126,7 +21378,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
@@ -21163,7 +21419,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
@@ -21200,7 +21460,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
@@ -21237,7 +21501,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
@@ -21274,7 +21542,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
@@ -21311,7 +21583,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
@@ -21348,7 +21624,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
@@ -21385,7 +21665,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
@@ -21422,7 +21706,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
@@ -23058,7 +23346,11 @@
           <t>41.0</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18775,12 +18775,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Austin Smotherman</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -18792,12 +18792,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18816,19 +18816,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -18898,29 +18898,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -18939,19 +18939,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -18980,29 +18980,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19021,29 +19021,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19062,29 +19062,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19103,29 +19103,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19144,19 +19144,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19185,19 +19185,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin Smotherman</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19226,29 +19226,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19267,29 +19267,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19308,19 +19308,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -19349,29 +19349,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -19390,29 +19390,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -19431,29 +19431,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -19472,29 +19472,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -19513,29 +19513,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -19554,29 +19554,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19595,29 +19595,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -19636,29 +19636,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -19677,29 +19677,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -19718,29 +19718,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -19759,29 +19759,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -19800,19 +19800,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -19841,29 +19841,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -19882,29 +19882,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -19923,29 +19923,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -19964,29 +19964,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -20005,29 +20005,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20058,17 +20058,17 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20099,7 +20099,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -20109,7 +20109,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -20140,17 +20140,17 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20181,17 +20181,17 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -20210,12 +20210,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -20227,12 +20227,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -20251,29 +20251,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -20292,29 +20292,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -20333,29 +20333,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -20415,7 +20415,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20427,7 +20427,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20468,17 +20468,17 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -20497,7 +20497,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20509,17 +20509,17 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20550,17 +20550,17 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20591,17 +20591,17 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20632,7 +20632,7 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dylan Frittelli</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20673,17 +20673,17 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20714,17 +20714,17 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20755,17 +20755,17 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20796,17 +20796,17 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -20825,12 +20825,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -20866,12 +20866,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -20907,29 +20907,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -20948,29 +20948,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -20989,29 +20989,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -21030,29 +21030,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -21071,29 +21071,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -21112,29 +21112,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -21153,12 +21153,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,29 +21194,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -21235,29 +21235,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,29 +21276,29 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,29 +21317,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,12 +21358,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -21375,12 +21375,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,29 +21440,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,29 +21481,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,29 +21522,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,29 +21563,29 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21604,12 +21604,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -21621,12 +21621,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -21645,29 +21645,29 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Dylan Frittelli</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -21686,29 +21686,29 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18816,29 +18816,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Séamus Power</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18857,29 +18857,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Séamus Power</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18910,17 +18910,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18951,17 +18951,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -18980,7 +18980,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greyson Sigg</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18992,17 +18992,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19021,7 +19021,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19033,17 +19033,17 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19115,17 +19115,17 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19197,17 +19197,17 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19238,17 +19238,17 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19267,29 +19267,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Greyson Sigg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19320,17 +19320,17 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19361,17 +19361,17 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -19390,29 +19390,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -19431,29 +19431,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -19472,19 +19472,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -19513,29 +19513,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>29.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -19554,19 +19554,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19607,17 +19607,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19648,17 +19648,17 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19689,17 +19689,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19730,7 +19730,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -19759,29 +19759,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -19800,19 +19800,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -19841,29 +19841,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zac Blair</t>
+          <t>Nick Dunlap</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19894,17 +19894,17 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>54.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19935,17 +19935,17 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Zac Blair</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19976,17 +19976,17 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20017,17 +20017,17 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -20046,29 +20046,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nick Dunlap</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -20087,29 +20087,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -20128,29 +20128,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20181,17 +20181,17 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>51.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -20210,7 +20210,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20222,17 +20222,17 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20263,17 +20263,17 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -20292,7 +20292,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20304,17 +20304,17 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -20333,7 +20333,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20345,7 +20345,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -20374,29 +20374,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -20415,29 +20415,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>68.0</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>56.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -20456,29 +20456,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -20497,7 +20497,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -20509,17 +20509,17 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20550,17 +20550,17 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -20579,29 +20579,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -20620,12 +20620,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -20637,12 +20637,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -20661,29 +20661,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -20702,19 +20702,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -20743,29 +20743,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -20784,12 +20784,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -20801,12 +20801,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -20825,12 +20825,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -20871,7 +20871,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -20907,29 +20907,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -20948,29 +20948,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>36.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -20989,29 +20989,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>70.0</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>36.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -21030,7 +21030,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jeremy Paul</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21047,12 +21047,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -21083,17 +21083,17 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -21112,29 +21112,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -21165,17 +21165,17 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21206,17 +21206,17 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -21235,7 +21235,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21247,17 +21247,17 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -21288,17 +21288,17 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,29 +21317,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,29 +21358,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21411,17 +21411,17 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,29 +21440,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,12 +21481,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,29 +21522,29 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nick Hardy</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>61.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,29 +21563,29 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21604,29 +21604,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Jeremy Paul</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -21667,7 +21667,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -21686,29 +21686,29 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Nick Hardy</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18797,7 +18797,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -18838,7 +18838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -18857,29 +18857,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ben Silverman</t>
+          <t>Taylor Moore</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taylor Moore</t>
+          <t>Ben Silverman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18910,17 +18910,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -18939,29 +18939,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chan Kim</t>
+          <t>Corey Conners</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -18980,7 +18980,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tom Hoge</t>
+          <t>Chan Kim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18992,17 +18992,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19021,7 +19021,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chris Kirk</t>
+          <t>Tom Hoge</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19033,7 +19033,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corey Conners</t>
+          <t>Chris Kirk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19074,7 +19074,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19103,29 +19103,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Luke Clanton</t>
+          <t>Danny Walker</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19144,29 +19144,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Chandler Blanchet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Luke Clanton</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19197,17 +19197,17 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Danny Walker</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19238,17 +19238,17 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>62.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Blanchet</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19279,17 +19279,17 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -19390,29 +19390,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rudy Sautron</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Adrien Dumont de Chassart</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19443,17 +19443,17 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Rudy Sautron</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19484,17 +19484,17 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -19513,7 +19513,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19525,12 +19525,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S.Y. Noh</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19571,12 +19571,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kihei Akina</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19607,17 +19607,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -19636,7 +19636,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ben Kohles</t>
+          <t>S.Y. Noh</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19648,17 +19648,17 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Davis Thompson</t>
+          <t>Kihei Akina</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19689,17 +19689,17 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>Ben Kohles</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19730,17 +19730,17 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Adrien Dumont de Chassart</t>
+          <t>Eric Cole</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20099,17 +20099,17 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -20128,29 +20128,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eric Cole</t>
+          <t>Davis Thompson</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20181,12 +20181,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -20210,7 +20210,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lucas Glover</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20222,17 +20222,17 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>70.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Neal Shipley</t>
+          <t>Lucas Glover</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20263,7 +20263,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -20292,7 +20292,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hayden Springer</t>
+          <t>Neal Shipley</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20304,12 +20304,12 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>68.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kristoffer Ventura</t>
+          <t>Hayden Springer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Kristoffer Ventura</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20391,12 +20391,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -20437,7 +20437,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -20456,7 +20456,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kensei Hirata</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20468,17 +20468,17 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -20497,29 +20497,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Kensei Hirata</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Takumi Kanaya</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20550,17 +20550,17 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20591,12 +20591,12 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20632,17 +20632,17 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20673,17 +20673,17 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andrew Novak</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20714,12 +20714,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ren Yonezawa</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20755,17 +20755,17 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -20784,7 +20784,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Andrew Novak</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20796,17 +20796,17 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -20825,29 +20825,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Ren Yonezawa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20919,12 +20919,12 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -20989,7 +20989,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Emiliano Grillo</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21001,17 +21001,17 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -21030,29 +21030,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin Eckroat</t>
+          <t>Emiliano Grillo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Erik van Rooyen</t>
+          <t>Vince Whaley</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -21083,17 +21083,17 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -21112,7 +21112,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Takumi Kanaya</t>
+          <t>Austin Eckroat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -21124,17 +21124,17 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -21153,7 +21153,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jeffrey Kang</t>
+          <t>Erik van Rooyen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -21165,17 +21165,17 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -21194,7 +21194,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Adam Svensson</t>
+          <t>Jeffrey Kang</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21206,12 +21206,12 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chad Ramey</t>
+          <t>Adam Svensson</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21247,17 +21247,17 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paul Peterson</t>
+          <t>Chad Ramey</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -21293,12 +21293,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kevin Roy</t>
+          <t>Paul Peterson</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -21329,17 +21329,17 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -21358,29 +21358,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vince Whaley</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hank Lebioda</t>
+          <t>Kevin Roy</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -21411,17 +21411,17 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jonathan Byrd</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21452,17 +21452,17 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Miles Russell</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -21493,17 +21493,17 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miles Russell</t>
+          <t>Hank Lebioda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -21534,17 +21534,17 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Jonathan Byrd</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21575,17 +21575,17 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18800,7 +18800,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18841,7 +18845,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18882,7 +18890,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18923,7 +18935,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18964,7 +18980,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19005,7 +19025,11 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19046,7 +19070,11 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19087,7 +19115,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19128,7 +19160,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19169,7 +19205,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19210,7 +19250,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19226,7 +19270,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19238,12 +19282,12 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -19251,7 +19295,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19267,7 +19315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19279,12 +19327,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -19292,7 +19340,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19333,7 +19385,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19349,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19361,12 +19417,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -19374,7 +19430,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19390,7 +19450,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19402,12 +19462,12 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -19415,7 +19475,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19456,7 +19520,11 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19497,7 +19565,11 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19513,7 +19585,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19525,12 +19597,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -19538,7 +19610,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19554,7 +19630,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19566,20 +19642,24 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19595,7 +19675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19607,12 +19687,12 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -19620,7 +19700,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19661,7 +19745,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19702,7 +19790,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19743,7 +19835,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19759,7 +19855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19771,12 +19867,12 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -19784,7 +19880,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19800,7 +19900,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19812,12 +19912,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -19825,7 +19925,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19841,7 +19945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19853,12 +19957,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -19866,7 +19970,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -19907,7 +20015,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -19923,7 +20035,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19935,12 +20047,12 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -19948,7 +20060,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -19989,7 +20105,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20005,7 +20125,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20017,20 +20137,24 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>30</t>
@@ -20046,7 +20170,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20058,20 +20182,24 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>64.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>30</t>
@@ -20112,7 +20240,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>27</t>
@@ -20153,7 +20285,11 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>33</t>
@@ -20169,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20181,20 +20317,24 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>69.0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>39</t>
@@ -20210,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20222,12 +20362,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -20235,7 +20375,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>--</t>
@@ -20276,7 +20420,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>--</t>
@@ -20317,7 +20465,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>--</t>
@@ -20358,7 +20510,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>--</t>
@@ -20399,7 +20555,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>--</t>
@@ -20415,7 +20575,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20427,20 +20587,24 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>--</t>
@@ -20456,7 +20620,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20468,20 +20632,24 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>--</t>
@@ -20522,7 +20690,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>--</t>
@@ -20563,7 +20735,11 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>--</t>
@@ -20579,7 +20755,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20591,12 +20767,12 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -20604,7 +20780,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>--</t>
@@ -20620,7 +20800,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20632,20 +20812,24 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>--</t>
@@ -20661,7 +20845,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20673,12 +20857,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -20686,7 +20870,11 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>--</t>
@@ -20702,7 +20890,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20714,12 +20902,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -20727,7 +20915,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>--</t>
@@ -20743,7 +20935,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20755,12 +20947,12 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -20768,7 +20960,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>--</t>
@@ -20809,7 +21005,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>--</t>
@@ -20850,7 +21050,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>--</t>
@@ -20866,7 +21070,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -20891,7 +21095,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>--</t>
@@ -20907,7 +21115,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -20932,7 +21140,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>--</t>
@@ -20948,7 +21160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -20960,12 +21172,12 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -20973,7 +21185,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>--</t>
@@ -20989,7 +21205,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21001,20 +21217,24 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>71.0</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>--</t>
@@ -21055,7 +21275,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>--</t>
@@ -21096,7 +21320,11 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>--</t>
@@ -21137,7 +21365,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>--</t>
@@ -21178,7 +21410,11 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>--</t>
@@ -21219,7 +21455,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>--</t>
@@ -21260,7 +21500,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>--</t>
@@ -21301,7 +21545,11 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>--</t>
@@ -21342,7 +21590,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>--</t>
@@ -21358,7 +21610,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21370,12 +21622,12 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -21383,7 +21635,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>--</t>
@@ -21424,7 +21680,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>--</t>
@@ -21440,7 +21700,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21452,12 +21712,12 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -21465,7 +21725,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>--</t>
@@ -21506,7 +21770,11 @@
           <t>73.0</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>--</t>
@@ -21547,7 +21815,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>--</t>
@@ -21588,7 +21860,11 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>--</t>
@@ -21629,7 +21905,11 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>--</t>
@@ -21670,7 +21950,11 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>--</t>
@@ -21711,7 +21995,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>--</t>

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Isaiah Salinda</t>
+          <t>Cam Davis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19282,12 +19282,12 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cam Davis</t>
+          <t>Isaiah Salinda</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19327,12 +19327,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denny McCarthy</t>
+          <t>David Skinns</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19417,12 +19417,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Skinns</t>
+          <t>Denny McCarthy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19462,12 +19462,12 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brice Garnett</t>
+          <t>Adam Hadwin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19597,12 +19597,12 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -19630,7 +19630,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Adam Hadwin</t>
+          <t>Dylan Wu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19642,12 +19642,12 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -19675,7 +19675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dylan Wu</t>
+          <t>Brice Garnett</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19687,12 +19687,12 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peter Malnati</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19867,12 +19867,12 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>David Ford</t>
+          <t>Peter Malnati</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19912,12 +19912,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Martin Laird</t>
+          <t>A.J. Ewart</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19957,12 +19957,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A.J. Ewart</t>
+          <t>Martin Laird</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -20047,12 +20047,12 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mackenzie Hughes</t>
+          <t>Jesper Svensson</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -20137,12 +20137,12 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>64.0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>69.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jesper Svensson</t>
+          <t>Mackenzie Hughes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -20182,12 +20182,12 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>69.0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>64.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Zecheng Dou</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -20317,12 +20317,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zecheng Dou</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20362,12 +20362,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trace Crowe</t>
+          <t>Mark Hubbard</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -20587,12 +20587,12 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>66.0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>67.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mark Hubbard</t>
+          <t>Trace Crowe</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -20632,12 +20632,12 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>67.0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>66.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Joel Dahmen</t>
+          <t>Max McGreevy</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -20767,12 +20767,12 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Max McGreevy</t>
+          <t>Lee Hodges</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -20812,12 +20812,12 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lee Hodges</t>
+          <t>Joel Dahmen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -20857,12 +20857,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Willie Mack III</t>
+          <t>Rafael Campos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20902,12 +20902,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rafael Campos</t>
+          <t>Willie Mack III</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -20947,12 +20947,12 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Robert Streb</t>
+          <t>Rico Hoey</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rico Hoey</t>
+          <t>Robert Streb</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Davis Riley</t>
+          <t>Davis Chatfield</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -21172,12 +21172,12 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -21205,7 +21205,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Davis Chatfield</t>
+          <t>Davis Riley</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21217,12 +21217,12 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Henrik Norlander</t>
+          <t>Brendon Todd</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21622,12 +21622,12 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brendon Todd</t>
+          <t>Henrik Norlander</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21712,12 +21712,12 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">

--- a/data/2027 Masters Draft & Scoreboard.xlsx
+++ b/data/2027 Masters Draft & Scoreboard.xlsx
@@ -18800,11 +18800,7 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>25</t>
@@ -18845,11 +18841,7 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>11</t>
@@ -18890,11 +18882,7 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>31</t>
@@ -18935,11 +18923,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>12</t>
@@ -18980,11 +18964,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>8</t>
@@ -19025,11 +19005,7 @@
           <t>64.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>3</t>
@@ -19070,11 +19046,7 @@
           <t>65.0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>3</t>
@@ -19115,11 +19087,7 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>27</t>
@@ -19160,11 +19128,7 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>23</t>
@@ -19205,11 +19169,7 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>23</t>
@@ -19250,11 +19210,7 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>23</t>
@@ -19295,11 +19251,7 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>20</t>
@@ -19340,11 +19292,7 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>13</t>
@@ -19385,11 +19333,7 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>9</t>
@@ -19430,11 +19374,7 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4</t>
@@ -19475,11 +19415,7 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>4</t>
@@ -19520,11 +19456,7 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4</t>
@@ -19565,11 +19497,7 @@
           <t>67.0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>4</t>
@@ -19610,11 +19538,7 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>28</t>
@@ -19655,11 +19579,7 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>24</t>
@@ -19700,11 +19620,7 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>21</t>
@@ -19745,11 +19661,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>21</t>
@@ -19790,11 +19702,7 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>17</t>
@@ -19835,11 +19743,7 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>17</t>
@@ -19880,11 +19784,7 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>10</t>
@@ -19925,11 +19825,7 @@
           <t>68.0</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>42</t>
@@ -19970,11 +19866,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>42</t>
@@ -20015,11 +19907,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>22</t>
@@ -20060,11 +19948,7 @@
           <t>69.0</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>18</t>
@@ -20105,11 +19989,7 @@
           <t>70.0</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>35</t>
@@ -20150,